--- a/outputs/01a00dfa-9be0-7871-990a-d6863466c203/蓟州区旅游经济政府数据扩充版_2010-2025.xlsx
+++ b/outputs/01a00dfa-9be0-7871-990a-d6863466c203/蓟州区旅游经济政府数据扩充版_2010-2025.xlsx
@@ -2,12 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="年度主表" sheetId="1" r:id="R88f5949570ad4e1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="旅游观测" sheetId="2" r:id="R0f89da7870d4424d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="宏观观测" sheetId="3" r:id="R2f94590ae8034da5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="相关指标" sheetId="4" r:id="Rf8a592965de84854"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源清单" sheetId="5" r:id="R7202c0b9bb504809"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与缺口" sheetId="6" r:id="R65662e00c78c458e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="年度主表" sheetId="1" r:id="R540db976a2e24950"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="旅游观测" sheetId="2" r:id="R1e604b42f2044bf6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="宏观观测" sheetId="3" r:id="R52a4fc97460c480e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="相关指标" sheetId="4" r:id="R9e5987afc8bf4cbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="供给能力" sheetId="5" r:id="Rd547df8d53b342e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="补缺线索" sheetId="6" r:id="Rcef7fe14267f4d7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源清单" sheetId="7" r:id="Rbf267ae8f17948c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与缺口" sheetId="8" r:id="Rfb8be66575db4354"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -233,6 +235,12 @@
     <x:xf numFmtId="200" fontId="1" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -299,9 +307,6 @@
     <x:xf numFmtId="200" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
@@ -315,9 +320,6 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -706,25 +708,30 @@
         <x:v>observed_rounded</x:v>
       </x:c>
       <x:c r="H4" s="18" t="str">
-        <x:v>333.3</x:v>
+        <x:v>291.52</x:v>
       </x:c>
       <x:c r="I4" s="24" t="str">
-        <x:v>provisional_estimate</x:v>
-      </x:c>
-      <x:c r="J4" s="18" t="str"/>
-      <x:c r="K4" s="24" t="str"/>
+        <x:v>official_yearbook</x:v>
+      </x:c>
+      <x:c r="J4" s="18" t="str">
+        <x:v>168.36</x:v>
+      </x:c>
+      <x:c r="K4" s="24" t="str">
+        <x:v>official_yearbook</x:v>
+      </x:c>
       <x:c r="L4" s="34" t="str">
-        <x:v>gov_jz_report_2013</x:v>
+        <x:v>gov_jz_report_2013;db_cei_jizhou_macro_20260817</x:v>
       </x:c>
       <x:c r="M4" s="34" t="str">
-        <x:v>旅游为工作报告回顾值；GDP为预计值且待后续年鉴复核</x:v>
+        <x:v>旅游为工作报告回顾值；宏观采用中经网天津统计年鉴回列值并由EPS交叉核验</x:v>
       </x:c>
       <x:c r="N4" s="22" t="n">
         <x:f>IF(OR(F4="",H4=""),"",F4/H4)</x:f>
-        <x:v>0.156015601560156</x:v>
-      </x:c>
-      <x:c r="O4" s="22" t="str">
+        <x:v>0.17837541163556533</x:v>
+      </x:c>
+      <x:c r="O4" s="22" t="n">
         <x:f>IF(OR(J4="",H4=""),"",J4/H4)</x:f>
+        <x:v>0.5775246981339188</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="23" customHeight="1">
@@ -750,30 +757,30 @@
         <x:v>observed_cached</x:v>
       </x:c>
       <x:c r="H5" s="18" t="str">
-        <x:v>316.8</x:v>
+        <x:v>316.84</x:v>
       </x:c>
       <x:c r="I5" s="24" t="str">
-        <x:v>inferred_from_official_bulletin</x:v>
+        <x:v>official_yearbook</x:v>
       </x:c>
       <x:c r="J5" s="18" t="str">
-        <x:v>187.5456</x:v>
+        <x:v>184.98</x:v>
       </x:c>
       <x:c r="K5" s="24" t="str">
-        <x:v>inferred_from_official_bulletin</x:v>
+        <x:v>official_yearbook</x:v>
       </x:c>
       <x:c r="L5" s="34" t="str">
-        <x:v>gov_jz_tourism_summary_2013;gov_jz_bulletin_2014</x:v>
+        <x:v>gov_jz_tourism_summary_2013;db_cei_jizhou_macro_20260817</x:v>
       </x:c>
       <x:c r="M5" s="34" t="str">
-        <x:v>旅游官方详情页当前下线；宏观值由2014公报回列信息推导</x:v>
+        <x:v>旅游官方详情页当前下线；宏观采用天津统计年鉴回列值</x:v>
       </x:c>
       <x:c r="N5" s="22" t="n">
         <x:f>IF(OR(F5="",H5=""),"",F5/H5)</x:f>
-        <x:v>0.1994949494949495</x:v>
+        <x:v>0.19946976391869717</x:v>
       </x:c>
       <x:c r="O5" s="22" t="n">
         <x:f>IF(OR(J5="",H5=""),"",J5/H5)</x:f>
-        <x:v>0.592</x:v>
+        <x:v>0.5838277995202626</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="23" customHeight="1">
@@ -799,30 +806,30 @@
         <x:v>observed</x:v>
       </x:c>
       <x:c r="H6" s="18" t="str">
-        <x:v>361.1</x:v>
+        <x:v>350.91</x:v>
       </x:c>
       <x:c r="I6" s="24" t="str">
-        <x:v>official_initial</x:v>
+        <x:v>official_yearbook</x:v>
       </x:c>
       <x:c r="J6" s="18" t="str">
-        <x:v>212.91</x:v>
+        <x:v>205.27</x:v>
       </x:c>
       <x:c r="K6" s="24" t="str">
-        <x:v>official_initial</x:v>
+        <x:v>official_yearbook</x:v>
       </x:c>
       <x:c r="L6" s="34" t="str">
-        <x:v>gov_jz_tourism_stats_2015;gov_jz_bulletin_2014</x:v>
+        <x:v>gov_jz_tourism_stats_2015;db_cei_jizhou_macro_20260817</x:v>
       </x:c>
       <x:c r="M6" s="34" t="str">
-        <x:v>游客和直接收入采用下一年统计表回列修订值</x:v>
+        <x:v>游客和直接收入采用下一年统计表回列修订值；宏观采用天津统计年鉴回列值</x:v>
       </x:c>
       <x:c r="N6" s="22" t="n">
         <x:f>IF(OR(F6="",H6=""),"",F6/H6)</x:f>
-        <x:v>0.21877596233730268</x:v>
+        <x:v>0.22512895044313355</x:v>
       </x:c>
       <x:c r="O6" s="22" t="n">
         <x:f>IF(OR(J6="",H6=""),"",J6/H6)</x:f>
-        <x:v>0.5896150650789255</x:v>
+        <x:v>0.5849648057906586</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="23" customHeight="1">
@@ -848,25 +855,30 @@
         <x:v>observed_supporting_attachment</x:v>
       </x:c>
       <x:c r="H7" s="18" t="str">
-        <x:v>409</x:v>
+        <x:v>390.54</x:v>
       </x:c>
       <x:c r="I7" s="24" t="str">
-        <x:v>provisional_estimate</x:v>
-      </x:c>
-      <x:c r="J7" s="18" t="str"/>
-      <x:c r="K7" s="24" t="str"/>
+        <x:v>official_yearbook</x:v>
+      </x:c>
+      <x:c r="J7" s="18" t="str">
+        <x:v>239.01</x:v>
+      </x:c>
+      <x:c r="K7" s="24" t="str">
+        <x:v>official_yearbook</x:v>
+      </x:c>
       <x:c r="L7" s="34" t="str">
-        <x:v>gov_jz_tourism_stats_2016;gov_jz_tourism_attachment_2015;gov_jz_report_2016</x:v>
+        <x:v>gov_jz_tourism_stats_2016;gov_jz_tourism_attachment_2015;db_cei_jizhou_macro_20260817</x:v>
       </x:c>
       <x:c r="M7" s="34" t="str">
-        <x:v>综合收入证据层级较低；GDP为十二五回顾值</x:v>
+        <x:v>综合收入证据层级较低；宏观采用天津统计年鉴回列值</x:v>
       </x:c>
       <x:c r="N7" s="22" t="n">
         <x:f>IF(OR(F7="",H7=""),"",F7/H7)</x:f>
-        <x:v>0.22982885085574573</x:v>
-      </x:c>
-      <x:c r="O7" s="22" t="str">
+        <x:v>0.24069237466072615</x:v>
+      </x:c>
+      <x:c r="O7" s="22" t="n">
         <x:f>IF(OR(J7="",H7=""),"",J7/H7)</x:f>
+        <x:v>0.6119987709325548</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="23" customHeight="1">
@@ -888,24 +900,29 @@
       <x:c r="F8" s="18" t="str"/>
       <x:c r="G8" s="24" t="str"/>
       <x:c r="H8" s="18" t="str">
-        <x:v>430</x:v>
+        <x:v>386.54</x:v>
       </x:c>
       <x:c r="I8" s="24" t="str">
-        <x:v>provisional_estimate</x:v>
-      </x:c>
-      <x:c r="J8" s="18" t="str"/>
-      <x:c r="K8" s="24" t="str"/>
+        <x:v>official_yearbook</x:v>
+      </x:c>
+      <x:c r="J8" s="18" t="str">
+        <x:v>228.44</x:v>
+      </x:c>
+      <x:c r="K8" s="24" t="str">
+        <x:v>official_yearbook</x:v>
+      </x:c>
       <x:c r="L8" s="34" t="str">
-        <x:v>gov_jz_tourism_stats_2017;gov_jz_report_2017</x:v>
+        <x:v>gov_jz_tourism_stats_2017;db_cei_jizhou_macro_20260817</x:v>
       </x:c>
       <x:c r="M8" s="34" t="str">
-        <x:v>未找到同口径综合收入；GDP为报告预计值</x:v>
+        <x:v>未找到同口径综合收入；宏观采用天津统计年鉴回列值</x:v>
       </x:c>
       <x:c r="N8" s="22" t="str">
         <x:f>IF(OR(F8="",H8=""),"",F8/H8)</x:f>
       </x:c>
-      <x:c r="O8" s="22" t="str">
+      <x:c r="O8" s="22" t="n">
         <x:f>IF(OR(J8="",H8=""),"",J8/H8)</x:f>
+        <x:v>0.5909867025404874</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="23" customHeight="1">
@@ -930,21 +947,31 @@
       <x:c r="G9" s="24" t="str">
         <x:v>observed_rounded</x:v>
       </x:c>
-      <x:c r="H9" s="18" t="str"/>
-      <x:c r="I9" s="24" t="str"/>
-      <x:c r="J9" s="18" t="str"/>
-      <x:c r="K9" s="24" t="str"/>
+      <x:c r="H9" s="18" t="str">
+        <x:v>365.42</x:v>
+      </x:c>
+      <x:c r="I9" s="24" t="str">
+        <x:v>official_yearbook</x:v>
+      </x:c>
+      <x:c r="J9" s="18" t="str">
+        <x:v>213.38</x:v>
+      </x:c>
+      <x:c r="K9" s="24" t="str">
+        <x:v>official_yearbook</x:v>
+      </x:c>
       <x:c r="L9" s="34" t="str">
-        <x:v>gov_jz_tourism_stats_2017;gov_jz_report_2018</x:v>
+        <x:v>gov_jz_tourism_stats_2017;gov_jz_report_2018;db_cei_jizhou_macro_20260817</x:v>
       </x:c>
       <x:c r="M9" s="34" t="str">
-        <x:v>工作报告游客约数2400未覆盖统计表精确值2392</x:v>
-      </x:c>
-      <x:c r="N9" s="22" t="str">
+        <x:v>工作报告游客约数2400未覆盖统计表精确值2392；宏观采用天津统计年鉴回列值</x:v>
+      </x:c>
+      <x:c r="N9" s="22" t="n">
         <x:f>IF(OR(F9="",H9=""),"",F9/H9)</x:f>
-      </x:c>
-      <x:c r="O9" s="22" t="str">
+        <x:v>0.355755021618959</x:v>
+      </x:c>
+      <x:c r="O9" s="22" t="n">
         <x:f>IF(OR(J9="",H9=""),"",J9/H9)</x:f>
+        <x:v>0.5839308193311805</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="23" customHeight="1">
@@ -966,25 +993,30 @@
         <x:v>observed_rounded</x:v>
       </x:c>
       <x:c r="H10" s="18" t="str">
-        <x:v>380</x:v>
+        <x:v>381.66</x:v>
       </x:c>
       <x:c r="I10" s="24" t="str">
-        <x:v>provisional_estimate</x:v>
-      </x:c>
-      <x:c r="J10" s="18" t="str"/>
-      <x:c r="K10" s="24" t="str"/>
+        <x:v>official_yearbook</x:v>
+      </x:c>
+      <x:c r="J10" s="18" t="str">
+        <x:v>234.32</x:v>
+      </x:c>
+      <x:c r="K10" s="24" t="str">
+        <x:v>official_yearbook</x:v>
+      </x:c>
       <x:c r="L10" s="34" t="str">
-        <x:v>gov_jz_report_2019</x:v>
+        <x:v>gov_jz_report_2019;db_cei_jizhou_macro_20260817</x:v>
       </x:c>
       <x:c r="M10" s="34" t="str">
-        <x:v>GDP为工作报告预计值</x:v>
+        <x:v>宏观采用中经网天津统计年鉴回列值并由EPS交叉核验</x:v>
       </x:c>
       <x:c r="N10" s="22" t="n">
         <x:f>IF(OR(F10="",H10=""),"",F10/H10)</x:f>
-        <x:v>0.3736842105263158</x:v>
-      </x:c>
-      <x:c r="O10" s="22" t="str">
+        <x:v>0.3720589005921501</x:v>
+      </x:c>
+      <x:c r="O10" s="22" t="n">
         <x:f>IF(OR(J10="",H10=""),"",J10/H10)</x:f>
+        <x:v>0.6139495886391028</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="23" customHeight="1">
@@ -1006,30 +1038,30 @@
         <x:v>observed_rounded</x:v>
       </x:c>
       <x:c r="H11" s="18" t="str">
-        <x:v>210.8</x:v>
+        <x:v>219.62</x:v>
       </x:c>
       <x:c r="I11" s="24" t="str">
-        <x:v>official_initial</x:v>
+        <x:v>official_yearbook</x:v>
       </x:c>
       <x:c r="J11" s="18" t="str">
-        <x:v>129.92</x:v>
+        <x:v>136.91</x:v>
       </x:c>
       <x:c r="K11" s="24" t="str">
-        <x:v>official_initial</x:v>
+        <x:v>official_yearbook</x:v>
       </x:c>
       <x:c r="L11" s="34" t="str">
-        <x:v>gov_jz_report_2020;gov_jz_bulletin_2019</x:v>
+        <x:v>gov_jz_report_2020;gov_jz_bulletin_2019;db_cei_jizhou_macro_20260817</x:v>
       </x:c>
       <x:c r="M11" s="34" t="str">
-        <x:v>宏观序列与2018年前口径存在明显断点</x:v>
+        <x:v>宏观采用天津统计年鉴回列值；与2018年相比仍存在明显口径断点</x:v>
       </x:c>
       <x:c r="N11" s="22" t="n">
         <x:f>IF(OR(F11="",H11=""),"",F11/H11)</x:f>
-        <x:v>0.7827324478178368</x:v>
+        <x:v>0.7512976960203989</x:v>
       </x:c>
       <x:c r="O11" s="22" t="n">
         <x:f>IF(OR(J11="",H11=""),"",J11/H11)</x:f>
-        <x:v>0.6163187855787475</x:v>
+        <x:v>0.6233949549221383</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="23" customHeight="1">
@@ -1043,29 +1075,29 @@
       <x:c r="F12" s="30" t="str"/>
       <x:c r="G12" s="31" t="str"/>
       <x:c r="H12" s="18" t="str">
-        <x:v>224.6</x:v>
+        <x:v>230.34</x:v>
       </x:c>
       <x:c r="I12" s="24" t="str">
-        <x:v>official_initial</x:v>
+        <x:v>official_yearbook</x:v>
       </x:c>
       <x:c r="J12" s="18" t="str">
-        <x:v>142.55</x:v>
+        <x:v>141.54</x:v>
       </x:c>
       <x:c r="K12" s="24" t="str">
-        <x:v>official_initial</x:v>
+        <x:v>official_yearbook</x:v>
       </x:c>
       <x:c r="L12" s="34" t="str">
-        <x:v>gov_jz_bulletin_2020</x:v>
+        <x:v>gov_jz_bulletin_2020;db_cei_jizhou_macro_20260817</x:v>
       </x:c>
       <x:c r="M12" s="34" t="str">
-        <x:v>疫情年份未找到可核验的年度旅游总量</x:v>
+        <x:v>疫情年份未找到可核验的年度旅游总量；宏观采用天津统计年鉴回列值</x:v>
       </x:c>
       <x:c r="N12" s="22" t="str">
         <x:f>IF(OR(F12="",H12=""),"",F12/H12)</x:f>
       </x:c>
       <x:c r="O12" s="22" t="n">
         <x:f>IF(OR(J12="",H12=""),"",J12/H12)</x:f>
-        <x:v>0.6346838824577027</x:v>
+        <x:v>0.6144829382651732</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="23" customHeight="1">
@@ -3643,83 +3675,83 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="16" t="str">
-        <x:v>2013</x:v>
+        <x:v>2012</x:v>
       </x:c>
       <x:c r="B10" s="6" t="str">
         <x:v>gdp</x:v>
       </x:c>
       <x:c r="C10" s="18" t="str">
-        <x:v>316.8</x:v>
+        <x:v>291.52</x:v>
       </x:c>
       <x:c r="D10" s="6" t="str">
         <x:v>100m_cny</x:v>
       </x:c>
       <x:c r="E10" s="24" t="str">
-        <x:v>inferred_from_official_bulletin</x:v>
+        <x:v>official_yearbook</x:v>
       </x:c>
       <x:c r="F10" s="24" t="str">
-        <x:v>2014_statistical_bulletin</x:v>
+        <x:v>2026_cei_tianjin_yearbook_series</x:v>
       </x:c>
       <x:c r="G10" s="6" t="str">
-        <x:v>gov_jz_bulletin_2014</x:v>
+        <x:v>db_cei_jizhou_macro_20260817</x:v>
       </x:c>
       <x:c r="H10" s="36" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="I10" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/zfxxgkqjjg/tjj1/fdzdgknr34/tjxx34/202012/t20201227_5212510.html</x:v>
+        <x:v>https://ceidata.cei.cn/db</x:v>
       </x:c>
       <x:c r="J10" s="34" t="str">
-        <x:v>由2014年361.1亿元减去公报所述比上年增加44.3亿元</x:v>
+        <x:v>中经网县域年度库直接显示且来源栏为天津统计年鉴；EPS同值交叉核验；优选</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="16" t="str">
-        <x:v>2013</x:v>
+        <x:v>2012</x:v>
       </x:c>
       <x:c r="B11" s="6" t="str">
         <x:v>tertiary_value_added</x:v>
       </x:c>
       <x:c r="C11" s="18" t="str">
-        <x:v>187.5456</x:v>
+        <x:v>168.36</x:v>
       </x:c>
       <x:c r="D11" s="6" t="str">
         <x:v>100m_cny</x:v>
       </x:c>
       <x:c r="E11" s="24" t="str">
-        <x:v>inferred_from_official_bulletin</x:v>
+        <x:v>official_yearbook</x:v>
       </x:c>
       <x:c r="F11" s="24" t="str">
-        <x:v>2014_statistical_bulletin</x:v>
+        <x:v>2026_cei_tianjin_yearbook_series</x:v>
       </x:c>
       <x:c r="G11" s="6" t="str">
-        <x:v>gov_jz_bulletin_2014</x:v>
+        <x:v>db_cei_jizhou_macro_20260817</x:v>
       </x:c>
       <x:c r="H11" s="36" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="I11" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/zfxxgkqjjg/tjj1/fdzdgknr34/tjxx34/202012/t20201227_5212510.html</x:v>
+        <x:v>https://ceidata.cei.cn/db</x:v>
       </x:c>
       <x:c r="J11" s="34" t="str">
-        <x:v>由2013年GDP316.8亿元乘公报回列三产占比59.2%</x:v>
+        <x:v>中经网县域年度库直接显示且来源栏为天津统计年鉴；EPS同值交叉核验；优选</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="16" t="str">
-        <x:v>2014</x:v>
+        <x:v>2013</x:v>
       </x:c>
       <x:c r="B12" s="6" t="str">
         <x:v>gdp</x:v>
       </x:c>
       <x:c r="C12" s="18" t="str">
-        <x:v>361.1</x:v>
+        <x:v>316.8</x:v>
       </x:c>
       <x:c r="D12" s="6" t="str">
         <x:v>100m_cny</x:v>
       </x:c>
       <x:c r="E12" s="24" t="str">
-        <x:v>official_initial</x:v>
+        <x:v>inferred_from_official_bulletin</x:v>
       </x:c>
       <x:c r="F12" s="24" t="str">
         <x:v>2014_statistical_bulletin</x:v>
@@ -3728,30 +3760,30 @@
         <x:v>gov_jz_bulletin_2014</x:v>
       </x:c>
       <x:c r="H12" s="36" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I12" s="34" t="str">
         <x:v>https://www.tjjz.gov.cn/zwgk/zfxxgkqjjg/tjj1/fdzdgknr34/tjxx34/202012/t20201227_5212510.html</x:v>
       </x:c>
       <x:c r="J12" s="34" t="str">
-        <x:v>初步核算值</x:v>
+        <x:v>由2014年361.1亿元减去公报所述比上年增加44.3亿元</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="16" t="str">
-        <x:v>2014</x:v>
+        <x:v>2013</x:v>
       </x:c>
       <x:c r="B13" s="6" t="str">
         <x:v>tertiary_value_added</x:v>
       </x:c>
       <x:c r="C13" s="18" t="str">
-        <x:v>212.91</x:v>
+        <x:v>187.5456</x:v>
       </x:c>
       <x:c r="D13" s="6" t="str">
         <x:v>100m_cny</x:v>
       </x:c>
       <x:c r="E13" s="24" t="str">
-        <x:v>official_initial</x:v>
+        <x:v>inferred_from_official_bulletin</x:v>
       </x:c>
       <x:c r="F13" s="24" t="str">
         <x:v>2014_statistical_bulletin</x:v>
@@ -3760,120 +3792,120 @@
         <x:v>gov_jz_bulletin_2014</x:v>
       </x:c>
       <x:c r="H13" s="36" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I13" s="34" t="str">
         <x:v>https://www.tjjz.gov.cn/zwgk/zfxxgkqjjg/tjj1/fdzdgknr34/tjxx34/202012/t20201227_5212510.html</x:v>
       </x:c>
       <x:c r="J13" s="34" t="str">
-        <x:v>初步核算值</x:v>
+        <x:v>由2013年GDP316.8亿元乘公报回列三产占比59.2%</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="16" t="str">
-        <x:v>2015</x:v>
+        <x:v>2013</x:v>
       </x:c>
       <x:c r="B14" s="6" t="str">
         <x:v>gdp</x:v>
       </x:c>
       <x:c r="C14" s="18" t="str">
-        <x:v>409</x:v>
+        <x:v>316.84</x:v>
       </x:c>
       <x:c r="D14" s="6" t="str">
         <x:v>100m_cny</x:v>
       </x:c>
       <x:c r="E14" s="24" t="str">
-        <x:v>provisional_estimate</x:v>
+        <x:v>official_yearbook</x:v>
       </x:c>
       <x:c r="F14" s="24" t="str">
-        <x:v>2016_government_report</x:v>
+        <x:v>2026_cei_tianjin_yearbook_series</x:v>
       </x:c>
       <x:c r="G14" s="6" t="str">
-        <x:v>gov_jz_report_2016</x:v>
+        <x:v>db_cei_jizhou_macro_20260817</x:v>
       </x:c>
       <x:c r="H14" s="36" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I14" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/ZFGZBG_20201207/202012/t20201227_5203179.html</x:v>
+        <x:v>https://ceidata.cei.cn/db</x:v>
       </x:c>
       <x:c r="J14" s="34" t="str">
-        <x:v>十二五回顾段中的期末值</x:v>
+        <x:v>中经网县域年度库直接显示且来源栏为天津统计年鉴；EPS同值交叉核验；优选</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="16" t="str">
-        <x:v>2016</x:v>
+        <x:v>2013</x:v>
       </x:c>
       <x:c r="B15" s="6" t="str">
-        <x:v>gdp</x:v>
+        <x:v>tertiary_value_added</x:v>
       </x:c>
       <x:c r="C15" s="18" t="str">
-        <x:v>430</x:v>
+        <x:v>184.98</x:v>
       </x:c>
       <x:c r="D15" s="6" t="str">
         <x:v>100m_cny</x:v>
       </x:c>
       <x:c r="E15" s="24" t="str">
-        <x:v>provisional_estimate</x:v>
+        <x:v>official_yearbook</x:v>
       </x:c>
       <x:c r="F15" s="24" t="str">
-        <x:v>2017_government_report</x:v>
+        <x:v>2026_cei_tianjin_yearbook_series</x:v>
       </x:c>
       <x:c r="G15" s="6" t="str">
-        <x:v>gov_jz_report_2017</x:v>
+        <x:v>db_cei_jizhou_macro_20260817</x:v>
       </x:c>
       <x:c r="H15" s="36" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I15" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/ZFGZBG_20201207/202012/t20201227_5203145.html</x:v>
+        <x:v>https://ceidata.cei.cn/db</x:v>
       </x:c>
       <x:c r="J15" s="34" t="str">
-        <x:v>报告预计值</x:v>
+        <x:v>中经网县域年度库直接显示且来源栏为天津统计年鉴；EPS同值交叉核验；优选</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="16" t="str">
-        <x:v>2018</x:v>
+        <x:v>2014</x:v>
       </x:c>
       <x:c r="B16" s="6" t="str">
         <x:v>gdp</x:v>
       </x:c>
       <x:c r="C16" s="18" t="str">
-        <x:v>380</x:v>
+        <x:v>361.1</x:v>
       </x:c>
       <x:c r="D16" s="6" t="str">
         <x:v>100m_cny</x:v>
       </x:c>
       <x:c r="E16" s="24" t="str">
-        <x:v>provisional_estimate</x:v>
+        <x:v>official_initial</x:v>
       </x:c>
       <x:c r="F16" s="24" t="str">
-        <x:v>2019_government_report</x:v>
+        <x:v>2014_statistical_bulletin</x:v>
       </x:c>
       <x:c r="G16" s="6" t="str">
-        <x:v>gov_jz_report_2019</x:v>
+        <x:v>gov_jz_bulletin_2014</x:v>
       </x:c>
       <x:c r="H16" s="36" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I16" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/ZFGZBG_20201207/202012/t20201227_5203369.html</x:v>
+        <x:v>https://www.tjjz.gov.cn/zwgk/zfxxgkqjjg/tjj1/fdzdgknr34/tjxx34/202012/t20201227_5212510.html</x:v>
       </x:c>
       <x:c r="J16" s="34" t="str">
-        <x:v>报告预计值</x:v>
+        <x:v>初步核算值</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="16" t="str">
-        <x:v>2019</x:v>
+        <x:v>2014</x:v>
       </x:c>
       <x:c r="B17" s="6" t="str">
-        <x:v>gdp</x:v>
+        <x:v>tertiary_value_added</x:v>
       </x:c>
       <x:c r="C17" s="18" t="str">
-        <x:v>210.8</x:v>
+        <x:v>212.91</x:v>
       </x:c>
       <x:c r="D17" s="6" t="str">
         <x:v>100m_cny</x:v>
@@ -3882,682 +3914,1258 @@
         <x:v>official_initial</x:v>
       </x:c>
       <x:c r="F17" s="24" t="str">
-        <x:v>2019_statistical_bulletin</x:v>
+        <x:v>2014_statistical_bulletin</x:v>
       </x:c>
       <x:c r="G17" s="6" t="str">
-        <x:v>gov_jz_bulletin_2019</x:v>
+        <x:v>gov_jz_bulletin_2014</x:v>
       </x:c>
       <x:c r="H17" s="36" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I17" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/zfxxgkqjjg/tjj1/fdzdgknr34/tjxx34/202107/t20210705_5495855.html</x:v>
+        <x:v>https://www.tjjz.gov.cn/zwgk/zfxxgkqjjg/tjj1/fdzdgknr34/tjxx34/202012/t20201227_5212510.html</x:v>
       </x:c>
       <x:c r="J17" s="34" t="str">
-        <x:v>统一核算前后历史序列存在明显断点</x:v>
+        <x:v>初步核算值</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="16" t="str">
-        <x:v>2019</x:v>
+        <x:v>2014</x:v>
       </x:c>
       <x:c r="B18" s="6" t="str">
-        <x:v>tertiary_value_added</x:v>
+        <x:v>gdp</x:v>
       </x:c>
       <x:c r="C18" s="18" t="str">
-        <x:v>129.92</x:v>
+        <x:v>350.91</x:v>
       </x:c>
       <x:c r="D18" s="6" t="str">
         <x:v>100m_cny</x:v>
       </x:c>
       <x:c r="E18" s="24" t="str">
-        <x:v>official_initial</x:v>
+        <x:v>official_yearbook</x:v>
       </x:c>
       <x:c r="F18" s="24" t="str">
-        <x:v>2019_statistical_bulletin</x:v>
+        <x:v>2026_cei_tianjin_yearbook_series</x:v>
       </x:c>
       <x:c r="G18" s="6" t="str">
-        <x:v>gov_jz_bulletin_2019</x:v>
+        <x:v>db_cei_jizhou_macro_20260817</x:v>
       </x:c>
       <x:c r="H18" s="36" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I18" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/zfxxgkqjjg/tjj1/fdzdgknr34/tjxx34/202107/t20210705_5495855.html</x:v>
-      </x:c>
-      <x:c r="J18" s="34" t="str"/>
+        <x:v>https://ceidata.cei.cn/db</x:v>
+      </x:c>
+      <x:c r="J18" s="34" t="str">
+        <x:v>中经网县域年度库直接显示且来源栏为天津统计年鉴；EPS同值交叉核验；优选</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="16" t="str">
-        <x:v>2020</x:v>
+        <x:v>2014</x:v>
       </x:c>
       <x:c r="B19" s="6" t="str">
-        <x:v>gdp</x:v>
+        <x:v>tertiary_value_added</x:v>
       </x:c>
       <x:c r="C19" s="18" t="str">
-        <x:v>224.6</x:v>
+        <x:v>205.27</x:v>
       </x:c>
       <x:c r="D19" s="6" t="str">
         <x:v>100m_cny</x:v>
       </x:c>
       <x:c r="E19" s="24" t="str">
-        <x:v>official_initial</x:v>
+        <x:v>official_yearbook</x:v>
       </x:c>
       <x:c r="F19" s="24" t="str">
-        <x:v>2020_statistical_bulletin</x:v>
+        <x:v>2026_cei_tianjin_yearbook_series</x:v>
       </x:c>
       <x:c r="G19" s="6" t="str">
-        <x:v>gov_jz_bulletin_2020</x:v>
+        <x:v>db_cei_jizhou_macro_20260817</x:v>
       </x:c>
       <x:c r="H19" s="36" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I19" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/zfxxgkqjjg/tjj1/fdzdgknr34/tjxx34/202111/t20211115_5703949.html</x:v>
-      </x:c>
-      <x:c r="J19" s="34" t="str"/>
+        <x:v>https://ceidata.cei.cn/db</x:v>
+      </x:c>
+      <x:c r="J19" s="34" t="str">
+        <x:v>中经网县域年度库直接显示且来源栏为天津统计年鉴；EPS同值交叉核验；优选</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="16" t="str">
-        <x:v>2020</x:v>
+        <x:v>2015</x:v>
       </x:c>
       <x:c r="B20" s="6" t="str">
-        <x:v>tertiary_value_added</x:v>
+        <x:v>gdp</x:v>
       </x:c>
       <x:c r="C20" s="18" t="str">
-        <x:v>142.55</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="D20" s="6" t="str">
         <x:v>100m_cny</x:v>
       </x:c>
       <x:c r="E20" s="24" t="str">
-        <x:v>official_initial</x:v>
+        <x:v>provisional_estimate</x:v>
       </x:c>
       <x:c r="F20" s="24" t="str">
-        <x:v>2020_statistical_bulletin</x:v>
+        <x:v>2016_government_report</x:v>
       </x:c>
       <x:c r="G20" s="6" t="str">
-        <x:v>gov_jz_bulletin_2020</x:v>
+        <x:v>gov_jz_report_2016</x:v>
       </x:c>
       <x:c r="H20" s="36" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I20" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/zfxxgkqjjg/tjj1/fdzdgknr34/tjxx34/202111/t20211115_5703949.html</x:v>
-      </x:c>
-      <x:c r="J20" s="34" t="str"/>
+        <x:v>https://www.tjjz.gov.cn/zwgk/ZFGZBG_20201207/202012/t20201227_5203179.html</x:v>
+      </x:c>
+      <x:c r="J20" s="34" t="str">
+        <x:v>十二五回顾段中的期末值</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="16" t="str">
-        <x:v>2021</x:v>
+        <x:v>2015</x:v>
       </x:c>
       <x:c r="B21" s="6" t="str">
         <x:v>gdp</x:v>
       </x:c>
       <x:c r="C21" s="18" t="str">
-        <x:v>250.4</x:v>
+        <x:v>390.54</x:v>
       </x:c>
       <x:c r="D21" s="6" t="str">
         <x:v>100m_cny</x:v>
       </x:c>
       <x:c r="E21" s="24" t="str">
-        <x:v>official_initial</x:v>
+        <x:v>official_yearbook</x:v>
       </x:c>
       <x:c r="F21" s="24" t="str">
-        <x:v>2021_statistical_bulletin</x:v>
+        <x:v>2026_cei_tianjin_yearbook_series</x:v>
       </x:c>
       <x:c r="G21" s="6" t="str">
-        <x:v>gov_jz_bulletin_2021</x:v>
+        <x:v>db_cei_jizhou_macro_20260817</x:v>
       </x:c>
       <x:c r="H21" s="36" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I21" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202211/t20221128_6044247.html</x:v>
+        <x:v>https://ceidata.cei.cn/db</x:v>
       </x:c>
       <x:c r="J21" s="34" t="str">
-        <x:v>公报初值</x:v>
+        <x:v>中经网县域年度库直接显示且来源栏为天津统计年鉴；EPS同值交叉核验；优选</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="16" t="str">
-        <x:v>2021</x:v>
+        <x:v>2015</x:v>
       </x:c>
       <x:c r="B22" s="6" t="str">
         <x:v>tertiary_value_added</x:v>
       </x:c>
       <x:c r="C22" s="18" t="str">
-        <x:v>151.52</x:v>
+        <x:v>239.01</x:v>
       </x:c>
       <x:c r="D22" s="6" t="str">
         <x:v>100m_cny</x:v>
       </x:c>
       <x:c r="E22" s="24" t="str">
-        <x:v>official_initial</x:v>
+        <x:v>official_yearbook</x:v>
       </x:c>
       <x:c r="F22" s="24" t="str">
-        <x:v>2021_statistical_bulletin</x:v>
+        <x:v>2026_cei_tianjin_yearbook_series</x:v>
       </x:c>
       <x:c r="G22" s="6" t="str">
-        <x:v>gov_jz_bulletin_2021</x:v>
+        <x:v>db_cei_jizhou_macro_20260817</x:v>
       </x:c>
       <x:c r="H22" s="36" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I22" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202211/t20221128_6044247.html</x:v>
+        <x:v>https://ceidata.cei.cn/db</x:v>
       </x:c>
       <x:c r="J22" s="34" t="str">
-        <x:v>公报初值</x:v>
+        <x:v>中经网县域年度库直接显示且来源栏为天津统计年鉴；EPS同值交叉核验；优选</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="16" t="str">
-        <x:v>2021</x:v>
+        <x:v>2016</x:v>
       </x:c>
       <x:c r="B23" s="6" t="str">
         <x:v>gdp</x:v>
       </x:c>
       <x:c r="C23" s="18" t="str">
-        <x:v>274.2034</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="D23" s="6" t="str">
         <x:v>100m_cny</x:v>
       </x:c>
       <x:c r="E23" s="24" t="str">
-        <x:v>official_revised</x:v>
+        <x:v>provisional_estimate</x:v>
       </x:c>
       <x:c r="F23" s="24" t="str">
-        <x:v>2022_jizhou_yearbook</x:v>
+        <x:v>2017_government_report</x:v>
       </x:c>
       <x:c r="G23" s="6" t="str">
-        <x:v>gov_jz_yearbook_2022</x:v>
+        <x:v>gov_jz_report_2017</x:v>
       </x:c>
       <x:c r="H23" s="36" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I23" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202311/W020250107625663560312.pdf</x:v>
+        <x:v>https://www.tjjz.gov.cn/zwgk/ZFGZBG_20201207/202012/t20201227_5203145.html</x:v>
       </x:c>
       <x:c r="J23" s="34" t="str">
-        <x:v>后版年鉴修订值；优选</x:v>
+        <x:v>报告预计值</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="16" t="str">
-        <x:v>2021</x:v>
+        <x:v>2016</x:v>
       </x:c>
       <x:c r="B24" s="6" t="str">
-        <x:v>tertiary_value_added</x:v>
+        <x:v>gdp</x:v>
       </x:c>
       <x:c r="C24" s="18" t="str">
-        <x:v>161.9732</x:v>
+        <x:v>386.54</x:v>
       </x:c>
       <x:c r="D24" s="6" t="str">
         <x:v>100m_cny</x:v>
       </x:c>
       <x:c r="E24" s="24" t="str">
-        <x:v>official_revised</x:v>
+        <x:v>official_yearbook</x:v>
       </x:c>
       <x:c r="F24" s="24" t="str">
-        <x:v>2022_jizhou_yearbook</x:v>
+        <x:v>2026_cei_tianjin_yearbook_series</x:v>
       </x:c>
       <x:c r="G24" s="6" t="str">
-        <x:v>gov_jz_yearbook_2022</x:v>
+        <x:v>db_cei_jizhou_macro_20260817</x:v>
       </x:c>
       <x:c r="H24" s="36" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I24" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202311/W020250107625663560312.pdf</x:v>
+        <x:v>https://ceidata.cei.cn/db</x:v>
       </x:c>
       <x:c r="J24" s="34" t="str">
-        <x:v>后版年鉴修订值；优选</x:v>
+        <x:v>中经网县域年度库直接显示且来源栏为天津统计年鉴；EPS同值交叉核验；优选</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="16" t="str">
-        <x:v>2022</x:v>
+        <x:v>2016</x:v>
       </x:c>
       <x:c r="B25" s="6" t="str">
-        <x:v>gdp</x:v>
+        <x:v>tertiary_value_added</x:v>
       </x:c>
       <x:c r="C25" s="18" t="str">
-        <x:v>279.33</x:v>
+        <x:v>228.44</x:v>
       </x:c>
       <x:c r="D25" s="6" t="str">
         <x:v>100m_cny</x:v>
       </x:c>
       <x:c r="E25" s="24" t="str">
-        <x:v>official_initial</x:v>
+        <x:v>official_yearbook</x:v>
       </x:c>
       <x:c r="F25" s="24" t="str">
-        <x:v>2022_statistical_bulletin</x:v>
+        <x:v>2026_cei_tianjin_yearbook_series</x:v>
       </x:c>
       <x:c r="G25" s="6" t="str">
-        <x:v>gov_jz_bulletin_2022</x:v>
+        <x:v>db_cei_jizhou_macro_20260817</x:v>
       </x:c>
       <x:c r="H25" s="36" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I25" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202311/t20231107_6450006.html</x:v>
+        <x:v>https://ceidata.cei.cn/db</x:v>
       </x:c>
       <x:c r="J25" s="34" t="str">
-        <x:v>公报初值</x:v>
+        <x:v>中经网县域年度库直接显示且来源栏为天津统计年鉴；EPS同值交叉核验；优选</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="16" t="str">
-        <x:v>2022</x:v>
+        <x:v>2017</x:v>
       </x:c>
       <x:c r="B26" s="6" t="str">
-        <x:v>tertiary_value_added</x:v>
+        <x:v>gdp</x:v>
       </x:c>
       <x:c r="C26" s="18" t="str">
-        <x:v>164.78</x:v>
+        <x:v>365.42</x:v>
       </x:c>
       <x:c r="D26" s="6" t="str">
         <x:v>100m_cny</x:v>
       </x:c>
       <x:c r="E26" s="24" t="str">
-        <x:v>official_initial</x:v>
+        <x:v>official_yearbook</x:v>
       </x:c>
       <x:c r="F26" s="24" t="str">
-        <x:v>2022_statistical_bulletin</x:v>
+        <x:v>2026_cei_tianjin_yearbook_series</x:v>
       </x:c>
       <x:c r="G26" s="6" t="str">
-        <x:v>gov_jz_bulletin_2022</x:v>
+        <x:v>db_cei_jizhou_macro_20260817</x:v>
       </x:c>
       <x:c r="H26" s="36" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I26" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202311/t20231107_6450006.html</x:v>
+        <x:v>https://ceidata.cei.cn/db</x:v>
       </x:c>
       <x:c r="J26" s="34" t="str">
-        <x:v>公报初值</x:v>
+        <x:v>中经网县域年度库直接显示且来源栏为天津统计年鉴；EPS同值交叉核验；优选</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="16" t="str">
-        <x:v>2022</x:v>
+        <x:v>2017</x:v>
       </x:c>
       <x:c r="B27" s="6" t="str">
-        <x:v>gdp</x:v>
+        <x:v>tertiary_value_added</x:v>
       </x:c>
       <x:c r="C27" s="18" t="str">
-        <x:v>282.2414</x:v>
+        <x:v>213.38</x:v>
       </x:c>
       <x:c r="D27" s="6" t="str">
         <x:v>100m_cny</x:v>
       </x:c>
       <x:c r="E27" s="24" t="str">
-        <x:v>official_revised</x:v>
+        <x:v>official_yearbook</x:v>
       </x:c>
       <x:c r="F27" s="24" t="str">
-        <x:v>2023_jizhou_yearbook</x:v>
+        <x:v>2026_cei_tianjin_yearbook_series</x:v>
       </x:c>
       <x:c r="G27" s="6" t="str">
-        <x:v>gov_jz_yearbook_2023</x:v>
+        <x:v>db_cei_jizhou_macro_20260817</x:v>
       </x:c>
       <x:c r="H27" s="36" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I27" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202501/W020250103638170510358.pdf</x:v>
+        <x:v>https://ceidata.cei.cn/db</x:v>
       </x:c>
       <x:c r="J27" s="34" t="str">
-        <x:v>后版年鉴修订值；优选</x:v>
+        <x:v>中经网县域年度库直接显示且来源栏为天津统计年鉴；EPS同值交叉核验；优选</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="16" t="str">
-        <x:v>2022</x:v>
+        <x:v>2018</x:v>
       </x:c>
       <x:c r="B28" s="6" t="str">
-        <x:v>tertiary_value_added</x:v>
+        <x:v>gdp</x:v>
       </x:c>
       <x:c r="C28" s="18" t="str">
-        <x:v>171.2106</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="D28" s="6" t="str">
         <x:v>100m_cny</x:v>
       </x:c>
       <x:c r="E28" s="24" t="str">
-        <x:v>official_revised</x:v>
+        <x:v>provisional_estimate</x:v>
       </x:c>
       <x:c r="F28" s="24" t="str">
-        <x:v>2023_jizhou_yearbook</x:v>
+        <x:v>2019_government_report</x:v>
       </x:c>
       <x:c r="G28" s="6" t="str">
-        <x:v>gov_jz_yearbook_2023</x:v>
+        <x:v>gov_jz_report_2019</x:v>
       </x:c>
       <x:c r="H28" s="36" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I28" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202501/W020250103638170510358.pdf</x:v>
+        <x:v>https://www.tjjz.gov.cn/zwgk/ZFGZBG_20201207/202012/t20201227_5203369.html</x:v>
       </x:c>
       <x:c r="J28" s="34" t="str">
-        <x:v>后版年鉴修订值；优选</x:v>
+        <x:v>报告预计值</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="16" t="str">
-        <x:v>2023</x:v>
+        <x:v>2018</x:v>
       </x:c>
       <x:c r="B29" s="6" t="str">
         <x:v>gdp</x:v>
       </x:c>
       <x:c r="C29" s="18" t="str">
-        <x:v>287.46</x:v>
+        <x:v>381.66</x:v>
       </x:c>
       <x:c r="D29" s="6" t="str">
         <x:v>100m_cny</x:v>
       </x:c>
       <x:c r="E29" s="24" t="str">
-        <x:v>official_initial</x:v>
+        <x:v>official_yearbook</x:v>
       </x:c>
       <x:c r="F29" s="24" t="str">
-        <x:v>2023_statistical_bulletin</x:v>
+        <x:v>2026_cei_tianjin_yearbook_series</x:v>
       </x:c>
       <x:c r="G29" s="6" t="str">
-        <x:v>gov_jz_bulletin_2023</x:v>
+        <x:v>db_cei_jizhou_macro_20260817</x:v>
       </x:c>
       <x:c r="H29" s="36" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I29" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/zfxxgkqjjg/tjj1/fdzdgknr34/tjxx34/202406/t20240627_6662772.html</x:v>
+        <x:v>https://ceidata.cei.cn/db</x:v>
       </x:c>
       <x:c r="J29" s="34" t="str">
-        <x:v>公报初值</x:v>
+        <x:v>中经网县域年度库直接显示且来源栏为天津统计年鉴；EPS同值交叉核验；优选</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="16" t="str">
-        <x:v>2023</x:v>
+        <x:v>2018</x:v>
       </x:c>
       <x:c r="B30" s="6" t="str">
         <x:v>tertiary_value_added</x:v>
       </x:c>
       <x:c r="C30" s="18" t="str">
-        <x:v>179.87</x:v>
+        <x:v>234.32</x:v>
       </x:c>
       <x:c r="D30" s="6" t="str">
         <x:v>100m_cny</x:v>
       </x:c>
       <x:c r="E30" s="24" t="str">
-        <x:v>official_initial</x:v>
+        <x:v>official_yearbook</x:v>
       </x:c>
       <x:c r="F30" s="24" t="str">
-        <x:v>2023_statistical_bulletin</x:v>
+        <x:v>2026_cei_tianjin_yearbook_series</x:v>
       </x:c>
       <x:c r="G30" s="6" t="str">
-        <x:v>gov_jz_bulletin_2023</x:v>
+        <x:v>db_cei_jizhou_macro_20260817</x:v>
       </x:c>
       <x:c r="H30" s="36" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I30" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/zfxxgkqjjg/tjj1/fdzdgknr34/tjxx34/202406/t20240627_6662772.html</x:v>
+        <x:v>https://ceidata.cei.cn/db</x:v>
       </x:c>
       <x:c r="J30" s="34" t="str">
-        <x:v>公报初值</x:v>
+        <x:v>中经网县域年度库直接显示且来源栏为天津统计年鉴；EPS同值交叉核验；优选</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="16" t="str">
-        <x:v>2023</x:v>
+        <x:v>2019</x:v>
       </x:c>
       <x:c r="B31" s="6" t="str">
         <x:v>gdp</x:v>
       </x:c>
       <x:c r="C31" s="18" t="str">
-        <x:v>288.3062</x:v>
+        <x:v>210.8</x:v>
       </x:c>
       <x:c r="D31" s="6" t="str">
         <x:v>100m_cny</x:v>
       </x:c>
       <x:c r="E31" s="24" t="str">
-        <x:v>official_final</x:v>
+        <x:v>official_initial</x:v>
       </x:c>
       <x:c r="F31" s="24" t="str">
-        <x:v>2024_jizhou_yearbook</x:v>
+        <x:v>2019_statistical_bulletin</x:v>
       </x:c>
       <x:c r="G31" s="6" t="str">
-        <x:v>gov_jz_yearbook_2024</x:v>
+        <x:v>gov_jz_bulletin_2019</x:v>
       </x:c>
       <x:c r="H31" s="36" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I31" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202511/W020251126560102082891.pdf</x:v>
+        <x:v>https://www.tjjz.gov.cn/zwgk/zfxxgkqjjg/tjj1/fdzdgknr34/tjxx34/202107/t20210705_5495855.html</x:v>
       </x:c>
       <x:c r="J31" s="34" t="str">
-        <x:v>后版年鉴最终核实值；优选</x:v>
+        <x:v>统一核算前后历史序列存在明显断点</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="16" t="str">
-        <x:v>2023</x:v>
+        <x:v>2019</x:v>
       </x:c>
       <x:c r="B32" s="6" t="str">
         <x:v>tertiary_value_added</x:v>
       </x:c>
       <x:c r="C32" s="18" t="str">
-        <x:v>176.1714</x:v>
+        <x:v>129.92</x:v>
       </x:c>
       <x:c r="D32" s="6" t="str">
         <x:v>100m_cny</x:v>
       </x:c>
       <x:c r="E32" s="24" t="str">
-        <x:v>official_final</x:v>
+        <x:v>official_initial</x:v>
       </x:c>
       <x:c r="F32" s="24" t="str">
-        <x:v>2024_jizhou_yearbook</x:v>
+        <x:v>2019_statistical_bulletin</x:v>
       </x:c>
       <x:c r="G32" s="6" t="str">
-        <x:v>gov_jz_yearbook_2024</x:v>
+        <x:v>gov_jz_bulletin_2019</x:v>
       </x:c>
       <x:c r="H32" s="36" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I32" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202511/W020251126560102082891.pdf</x:v>
-      </x:c>
-      <x:c r="J32" s="34" t="str">
-        <x:v>后版年鉴最终核实值；优选</x:v>
-      </x:c>
+        <x:v>https://www.tjjz.gov.cn/zwgk/zfxxgkqjjg/tjj1/fdzdgknr34/tjxx34/202107/t20210705_5495855.html</x:v>
+      </x:c>
+      <x:c r="J32" s="34" t="str"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="16" t="str">
-        <x:v>2024</x:v>
+        <x:v>2019</x:v>
       </x:c>
       <x:c r="B33" s="6" t="str">
         <x:v>gdp</x:v>
       </x:c>
       <x:c r="C33" s="18" t="str">
-        <x:v>298.87</x:v>
+        <x:v>219.62</x:v>
       </x:c>
       <x:c r="D33" s="6" t="str">
         <x:v>100m_cny</x:v>
       </x:c>
       <x:c r="E33" s="24" t="str">
-        <x:v>official_initial</x:v>
+        <x:v>official_yearbook</x:v>
       </x:c>
       <x:c r="F33" s="24" t="str">
-        <x:v>2024_statistical_bulletin</x:v>
+        <x:v>2026_cei_tianjin_yearbook_series</x:v>
       </x:c>
       <x:c r="G33" s="6" t="str">
-        <x:v>gov_jz_bulletin_2024</x:v>
+        <x:v>db_cei_jizhou_macro_20260817</x:v>
       </x:c>
       <x:c r="H33" s="36" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I33" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202506/t20250630_6969506.html</x:v>
+        <x:v>https://ceidata.cei.cn/db</x:v>
       </x:c>
       <x:c r="J33" s="34" t="str">
-        <x:v>公报初值</x:v>
+        <x:v>天津统计年鉴回列值；2018—2019仍有显著口径断点；优选</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="16" t="str">
-        <x:v>2024</x:v>
+        <x:v>2019</x:v>
       </x:c>
       <x:c r="B34" s="6" t="str">
         <x:v>tertiary_value_added</x:v>
       </x:c>
       <x:c r="C34" s="18" t="str">
-        <x:v>183.97</x:v>
+        <x:v>136.91</x:v>
       </x:c>
       <x:c r="D34" s="6" t="str">
         <x:v>100m_cny</x:v>
       </x:c>
       <x:c r="E34" s="24" t="str">
-        <x:v>official_initial</x:v>
+        <x:v>official_yearbook</x:v>
       </x:c>
       <x:c r="F34" s="24" t="str">
-        <x:v>2024_statistical_bulletin</x:v>
+        <x:v>2026_cei_tianjin_yearbook_series</x:v>
       </x:c>
       <x:c r="G34" s="6" t="str">
-        <x:v>gov_jz_bulletin_2024</x:v>
+        <x:v>db_cei_jizhou_macro_20260817</x:v>
       </x:c>
       <x:c r="H34" s="36" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I34" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202506/t20250630_6969506.html</x:v>
+        <x:v>https://ceidata.cei.cn/db</x:v>
       </x:c>
       <x:c r="J34" s="34" t="str">
-        <x:v>公报初值</x:v>
+        <x:v>天津统计年鉴回列值；2018—2019仍有显著口径断点；优选</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="16" t="str">
-        <x:v>2024</x:v>
+        <x:v>2020</x:v>
       </x:c>
       <x:c r="B35" s="6" t="str">
         <x:v>gdp</x:v>
       </x:c>
       <x:c r="C35" s="18" t="str">
-        <x:v>298.865</x:v>
+        <x:v>224.6</x:v>
       </x:c>
       <x:c r="D35" s="6" t="str">
         <x:v>100m_cny</x:v>
       </x:c>
       <x:c r="E35" s="24" t="str">
-        <x:v>official_yearbook</x:v>
+        <x:v>official_initial</x:v>
       </x:c>
       <x:c r="F35" s="24" t="str">
-        <x:v>2024_jizhou_yearbook</x:v>
+        <x:v>2020_statistical_bulletin</x:v>
       </x:c>
       <x:c r="G35" s="6" t="str">
-        <x:v>gov_jz_yearbook_2024</x:v>
+        <x:v>gov_jz_bulletin_2020</x:v>
       </x:c>
       <x:c r="H35" s="36" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I35" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202511/W020251126560102082891.pdf</x:v>
-      </x:c>
-      <x:c r="J35" s="34" t="str">
-        <x:v>年鉴现价值；优选</x:v>
-      </x:c>
+        <x:v>https://www.tjjz.gov.cn/zwgk/zfxxgkqjjg/tjj1/fdzdgknr34/tjxx34/202111/t20211115_5703949.html</x:v>
+      </x:c>
+      <x:c r="J35" s="34" t="str"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="16" t="str">
-        <x:v>2024</x:v>
+        <x:v>2020</x:v>
       </x:c>
       <x:c r="B36" s="6" t="str">
         <x:v>tertiary_value_added</x:v>
       </x:c>
       <x:c r="C36" s="18" t="str">
-        <x:v>183.9654</x:v>
+        <x:v>142.55</x:v>
       </x:c>
       <x:c r="D36" s="6" t="str">
         <x:v>100m_cny</x:v>
       </x:c>
       <x:c r="E36" s="24" t="str">
-        <x:v>official_yearbook</x:v>
+        <x:v>official_initial</x:v>
       </x:c>
       <x:c r="F36" s="24" t="str">
-        <x:v>2024_jizhou_yearbook</x:v>
+        <x:v>2020_statistical_bulletin</x:v>
       </x:c>
       <x:c r="G36" s="6" t="str">
-        <x:v>gov_jz_yearbook_2024</x:v>
+        <x:v>gov_jz_bulletin_2020</x:v>
       </x:c>
       <x:c r="H36" s="36" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I36" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202511/W020251126560102082891.pdf</x:v>
-      </x:c>
-      <x:c r="J36" s="34" t="str">
-        <x:v>年鉴现价值；优选</x:v>
-      </x:c>
+        <x:v>https://www.tjjz.gov.cn/zwgk/zfxxgkqjjg/tjj1/fdzdgknr34/tjxx34/202111/t20211115_5703949.html</x:v>
+      </x:c>
+      <x:c r="J36" s="34" t="str"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="16" t="str">
-        <x:v>2025</x:v>
+        <x:v>2020</x:v>
       </x:c>
       <x:c r="B37" s="6" t="str">
         <x:v>gdp</x:v>
       </x:c>
       <x:c r="C37" s="18" t="str">
-        <x:v>311.94</x:v>
+        <x:v>230.34</x:v>
       </x:c>
       <x:c r="D37" s="6" t="str">
         <x:v>100m_cny</x:v>
       </x:c>
       <x:c r="E37" s="24" t="str">
-        <x:v>official_initial</x:v>
+        <x:v>official_yearbook</x:v>
       </x:c>
       <x:c r="F37" s="24" t="str">
-        <x:v>2025_statistical_bulletin</x:v>
+        <x:v>2026_cei_tianjin_yearbook_series</x:v>
       </x:c>
       <x:c r="G37" s="6" t="str">
-        <x:v>gov_jz_bulletin_2025</x:v>
+        <x:v>db_cei_jizhou_macro_20260817</x:v>
       </x:c>
       <x:c r="H37" s="36" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I37" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202606/t20260629_7325623.html</x:v>
-      </x:c>
-      <x:c r="J37" s="34" t="str"/>
+        <x:v>https://ceidata.cei.cn/db</x:v>
+      </x:c>
+      <x:c r="J37" s="34" t="str">
+        <x:v>天津统计年鉴回列值；EPS交叉核验；优选</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="16" t="str">
-        <x:v>2025</x:v>
+        <x:v>2020</x:v>
       </x:c>
       <x:c r="B38" s="6" t="str">
         <x:v>tertiary_value_added</x:v>
       </x:c>
       <x:c r="C38" s="18" t="str">
+        <x:v>141.54</x:v>
+      </x:c>
+      <x:c r="D38" s="6" t="str">
+        <x:v>100m_cny</x:v>
+      </x:c>
+      <x:c r="E38" s="24" t="str">
+        <x:v>official_yearbook</x:v>
+      </x:c>
+      <x:c r="F38" s="24" t="str">
+        <x:v>2026_cei_tianjin_yearbook_series</x:v>
+      </x:c>
+      <x:c r="G38" s="6" t="str">
+        <x:v>db_cei_jizhou_macro_20260817</x:v>
+      </x:c>
+      <x:c r="H38" s="36" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I38" s="34" t="str">
+        <x:v>https://ceidata.cei.cn/db</x:v>
+      </x:c>
+      <x:c r="J38" s="34" t="str">
+        <x:v>天津统计年鉴回列值；EPS交叉核验；优选</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="16" t="str">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="B39" s="6" t="str">
+        <x:v>gdp</x:v>
+      </x:c>
+      <x:c r="C39" s="18" t="str">
+        <x:v>250.4</x:v>
+      </x:c>
+      <x:c r="D39" s="6" t="str">
+        <x:v>100m_cny</x:v>
+      </x:c>
+      <x:c r="E39" s="24" t="str">
+        <x:v>official_initial</x:v>
+      </x:c>
+      <x:c r="F39" s="24" t="str">
+        <x:v>2021_statistical_bulletin</x:v>
+      </x:c>
+      <x:c r="G39" s="6" t="str">
+        <x:v>gov_jz_bulletin_2021</x:v>
+      </x:c>
+      <x:c r="H39" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I39" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202211/t20221128_6044247.html</x:v>
+      </x:c>
+      <x:c r="J39" s="34" t="str">
+        <x:v>公报初值</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="16" t="str">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="B40" s="6" t="str">
+        <x:v>tertiary_value_added</x:v>
+      </x:c>
+      <x:c r="C40" s="18" t="str">
+        <x:v>151.52</x:v>
+      </x:c>
+      <x:c r="D40" s="6" t="str">
+        <x:v>100m_cny</x:v>
+      </x:c>
+      <x:c r="E40" s="24" t="str">
+        <x:v>official_initial</x:v>
+      </x:c>
+      <x:c r="F40" s="24" t="str">
+        <x:v>2021_statistical_bulletin</x:v>
+      </x:c>
+      <x:c r="G40" s="6" t="str">
+        <x:v>gov_jz_bulletin_2021</x:v>
+      </x:c>
+      <x:c r="H40" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I40" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202211/t20221128_6044247.html</x:v>
+      </x:c>
+      <x:c r="J40" s="34" t="str">
+        <x:v>公报初值</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="16" t="str">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="B41" s="6" t="str">
+        <x:v>gdp</x:v>
+      </x:c>
+      <x:c r="C41" s="18" t="str">
+        <x:v>274.2034</x:v>
+      </x:c>
+      <x:c r="D41" s="6" t="str">
+        <x:v>100m_cny</x:v>
+      </x:c>
+      <x:c r="E41" s="24" t="str">
+        <x:v>official_revised</x:v>
+      </x:c>
+      <x:c r="F41" s="24" t="str">
+        <x:v>2022_jizhou_yearbook</x:v>
+      </x:c>
+      <x:c r="G41" s="6" t="str">
+        <x:v>gov_jz_yearbook_2022</x:v>
+      </x:c>
+      <x:c r="H41" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I41" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202311/W020250107625663560312.pdf</x:v>
+      </x:c>
+      <x:c r="J41" s="34" t="str">
+        <x:v>后版年鉴修订值；优选</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="16" t="str">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="B42" s="6" t="str">
+        <x:v>tertiary_value_added</x:v>
+      </x:c>
+      <x:c r="C42" s="18" t="str">
+        <x:v>161.9732</x:v>
+      </x:c>
+      <x:c r="D42" s="6" t="str">
+        <x:v>100m_cny</x:v>
+      </x:c>
+      <x:c r="E42" s="24" t="str">
+        <x:v>official_revised</x:v>
+      </x:c>
+      <x:c r="F42" s="24" t="str">
+        <x:v>2022_jizhou_yearbook</x:v>
+      </x:c>
+      <x:c r="G42" s="6" t="str">
+        <x:v>gov_jz_yearbook_2022</x:v>
+      </x:c>
+      <x:c r="H42" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I42" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202311/W020250107625663560312.pdf</x:v>
+      </x:c>
+      <x:c r="J42" s="34" t="str">
+        <x:v>后版年鉴修订值；优选</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="16" t="str">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="B43" s="6" t="str">
+        <x:v>gdp</x:v>
+      </x:c>
+      <x:c r="C43" s="18" t="str">
+        <x:v>279.33</x:v>
+      </x:c>
+      <x:c r="D43" s="6" t="str">
+        <x:v>100m_cny</x:v>
+      </x:c>
+      <x:c r="E43" s="24" t="str">
+        <x:v>official_initial</x:v>
+      </x:c>
+      <x:c r="F43" s="24" t="str">
+        <x:v>2022_statistical_bulletin</x:v>
+      </x:c>
+      <x:c r="G43" s="6" t="str">
+        <x:v>gov_jz_bulletin_2022</x:v>
+      </x:c>
+      <x:c r="H43" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I43" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202311/t20231107_6450006.html</x:v>
+      </x:c>
+      <x:c r="J43" s="34" t="str">
+        <x:v>公报初值</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="16" t="str">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="B44" s="6" t="str">
+        <x:v>tertiary_value_added</x:v>
+      </x:c>
+      <x:c r="C44" s="18" t="str">
+        <x:v>164.78</x:v>
+      </x:c>
+      <x:c r="D44" s="6" t="str">
+        <x:v>100m_cny</x:v>
+      </x:c>
+      <x:c r="E44" s="24" t="str">
+        <x:v>official_initial</x:v>
+      </x:c>
+      <x:c r="F44" s="24" t="str">
+        <x:v>2022_statistical_bulletin</x:v>
+      </x:c>
+      <x:c r="G44" s="6" t="str">
+        <x:v>gov_jz_bulletin_2022</x:v>
+      </x:c>
+      <x:c r="H44" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I44" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202311/t20231107_6450006.html</x:v>
+      </x:c>
+      <x:c r="J44" s="34" t="str">
+        <x:v>公报初值</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="16" t="str">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="B45" s="6" t="str">
+        <x:v>gdp</x:v>
+      </x:c>
+      <x:c r="C45" s="18" t="str">
+        <x:v>282.2414</x:v>
+      </x:c>
+      <x:c r="D45" s="6" t="str">
+        <x:v>100m_cny</x:v>
+      </x:c>
+      <x:c r="E45" s="24" t="str">
+        <x:v>official_revised</x:v>
+      </x:c>
+      <x:c r="F45" s="24" t="str">
+        <x:v>2023_jizhou_yearbook</x:v>
+      </x:c>
+      <x:c r="G45" s="6" t="str">
+        <x:v>gov_jz_yearbook_2023</x:v>
+      </x:c>
+      <x:c r="H45" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I45" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202501/W020250103638170510358.pdf</x:v>
+      </x:c>
+      <x:c r="J45" s="34" t="str">
+        <x:v>后版年鉴修订值；优选</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="16" t="str">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="B46" s="6" t="str">
+        <x:v>tertiary_value_added</x:v>
+      </x:c>
+      <x:c r="C46" s="18" t="str">
+        <x:v>171.2106</x:v>
+      </x:c>
+      <x:c r="D46" s="6" t="str">
+        <x:v>100m_cny</x:v>
+      </x:c>
+      <x:c r="E46" s="24" t="str">
+        <x:v>official_revised</x:v>
+      </x:c>
+      <x:c r="F46" s="24" t="str">
+        <x:v>2023_jizhou_yearbook</x:v>
+      </x:c>
+      <x:c r="G46" s="6" t="str">
+        <x:v>gov_jz_yearbook_2023</x:v>
+      </x:c>
+      <x:c r="H46" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I46" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202501/W020250103638170510358.pdf</x:v>
+      </x:c>
+      <x:c r="J46" s="34" t="str">
+        <x:v>后版年鉴修订值；优选</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="16" t="str">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="B47" s="6" t="str">
+        <x:v>gdp</x:v>
+      </x:c>
+      <x:c r="C47" s="18" t="str">
+        <x:v>287.46</x:v>
+      </x:c>
+      <x:c r="D47" s="6" t="str">
+        <x:v>100m_cny</x:v>
+      </x:c>
+      <x:c r="E47" s="24" t="str">
+        <x:v>official_initial</x:v>
+      </x:c>
+      <x:c r="F47" s="24" t="str">
+        <x:v>2023_statistical_bulletin</x:v>
+      </x:c>
+      <x:c r="G47" s="6" t="str">
+        <x:v>gov_jz_bulletin_2023</x:v>
+      </x:c>
+      <x:c r="H47" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I47" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/zfxxgkqjjg/tjj1/fdzdgknr34/tjxx34/202406/t20240627_6662772.html</x:v>
+      </x:c>
+      <x:c r="J47" s="34" t="str">
+        <x:v>公报初值</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="16" t="str">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="B48" s="6" t="str">
+        <x:v>tertiary_value_added</x:v>
+      </x:c>
+      <x:c r="C48" s="18" t="str">
+        <x:v>179.87</x:v>
+      </x:c>
+      <x:c r="D48" s="6" t="str">
+        <x:v>100m_cny</x:v>
+      </x:c>
+      <x:c r="E48" s="24" t="str">
+        <x:v>official_initial</x:v>
+      </x:c>
+      <x:c r="F48" s="24" t="str">
+        <x:v>2023_statistical_bulletin</x:v>
+      </x:c>
+      <x:c r="G48" s="6" t="str">
+        <x:v>gov_jz_bulletin_2023</x:v>
+      </x:c>
+      <x:c r="H48" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I48" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/zfxxgkqjjg/tjj1/fdzdgknr34/tjxx34/202406/t20240627_6662772.html</x:v>
+      </x:c>
+      <x:c r="J48" s="34" t="str">
+        <x:v>公报初值</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="16" t="str">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="B49" s="6" t="str">
+        <x:v>gdp</x:v>
+      </x:c>
+      <x:c r="C49" s="18" t="str">
+        <x:v>288.3062</x:v>
+      </x:c>
+      <x:c r="D49" s="6" t="str">
+        <x:v>100m_cny</x:v>
+      </x:c>
+      <x:c r="E49" s="24" t="str">
+        <x:v>official_final</x:v>
+      </x:c>
+      <x:c r="F49" s="24" t="str">
+        <x:v>2024_jizhou_yearbook</x:v>
+      </x:c>
+      <x:c r="G49" s="6" t="str">
+        <x:v>gov_jz_yearbook_2024</x:v>
+      </x:c>
+      <x:c r="H49" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I49" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202511/W020251126560102082891.pdf</x:v>
+      </x:c>
+      <x:c r="J49" s="34" t="str">
+        <x:v>后版年鉴最终核实值；优选</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="16" t="str">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="B50" s="6" t="str">
+        <x:v>tertiary_value_added</x:v>
+      </x:c>
+      <x:c r="C50" s="18" t="str">
+        <x:v>176.1714</x:v>
+      </x:c>
+      <x:c r="D50" s="6" t="str">
+        <x:v>100m_cny</x:v>
+      </x:c>
+      <x:c r="E50" s="24" t="str">
+        <x:v>official_final</x:v>
+      </x:c>
+      <x:c r="F50" s="24" t="str">
+        <x:v>2024_jizhou_yearbook</x:v>
+      </x:c>
+      <x:c r="G50" s="6" t="str">
+        <x:v>gov_jz_yearbook_2024</x:v>
+      </x:c>
+      <x:c r="H50" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I50" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202511/W020251126560102082891.pdf</x:v>
+      </x:c>
+      <x:c r="J50" s="34" t="str">
+        <x:v>后版年鉴最终核实值；优选</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="16" t="str">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B51" s="6" t="str">
+        <x:v>gdp</x:v>
+      </x:c>
+      <x:c r="C51" s="18" t="str">
+        <x:v>298.87</x:v>
+      </x:c>
+      <x:c r="D51" s="6" t="str">
+        <x:v>100m_cny</x:v>
+      </x:c>
+      <x:c r="E51" s="24" t="str">
+        <x:v>official_initial</x:v>
+      </x:c>
+      <x:c r="F51" s="24" t="str">
+        <x:v>2024_statistical_bulletin</x:v>
+      </x:c>
+      <x:c r="G51" s="6" t="str">
+        <x:v>gov_jz_bulletin_2024</x:v>
+      </x:c>
+      <x:c r="H51" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I51" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202506/t20250630_6969506.html</x:v>
+      </x:c>
+      <x:c r="J51" s="34" t="str">
+        <x:v>公报初值</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="16" t="str">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B52" s="6" t="str">
+        <x:v>tertiary_value_added</x:v>
+      </x:c>
+      <x:c r="C52" s="18" t="str">
+        <x:v>183.97</x:v>
+      </x:c>
+      <x:c r="D52" s="6" t="str">
+        <x:v>100m_cny</x:v>
+      </x:c>
+      <x:c r="E52" s="24" t="str">
+        <x:v>official_initial</x:v>
+      </x:c>
+      <x:c r="F52" s="24" t="str">
+        <x:v>2024_statistical_bulletin</x:v>
+      </x:c>
+      <x:c r="G52" s="6" t="str">
+        <x:v>gov_jz_bulletin_2024</x:v>
+      </x:c>
+      <x:c r="H52" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I52" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202506/t20250630_6969506.html</x:v>
+      </x:c>
+      <x:c r="J52" s="34" t="str">
+        <x:v>公报初值</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="16" t="str">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B53" s="6" t="str">
+        <x:v>gdp</x:v>
+      </x:c>
+      <x:c r="C53" s="18" t="str">
+        <x:v>298.865</x:v>
+      </x:c>
+      <x:c r="D53" s="6" t="str">
+        <x:v>100m_cny</x:v>
+      </x:c>
+      <x:c r="E53" s="24" t="str">
+        <x:v>official_yearbook</x:v>
+      </x:c>
+      <x:c r="F53" s="24" t="str">
+        <x:v>2024_jizhou_yearbook</x:v>
+      </x:c>
+      <x:c r="G53" s="6" t="str">
+        <x:v>gov_jz_yearbook_2024</x:v>
+      </x:c>
+      <x:c r="H53" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I53" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202511/W020251126560102082891.pdf</x:v>
+      </x:c>
+      <x:c r="J53" s="34" t="str">
+        <x:v>年鉴现价值；优选</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="16" t="str">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B54" s="6" t="str">
+        <x:v>tertiary_value_added</x:v>
+      </x:c>
+      <x:c r="C54" s="18" t="str">
+        <x:v>183.9654</x:v>
+      </x:c>
+      <x:c r="D54" s="6" t="str">
+        <x:v>100m_cny</x:v>
+      </x:c>
+      <x:c r="E54" s="24" t="str">
+        <x:v>official_yearbook</x:v>
+      </x:c>
+      <x:c r="F54" s="24" t="str">
+        <x:v>2024_jizhou_yearbook</x:v>
+      </x:c>
+      <x:c r="G54" s="6" t="str">
+        <x:v>gov_jz_yearbook_2024</x:v>
+      </x:c>
+      <x:c r="H54" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I54" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202511/W020251126560102082891.pdf</x:v>
+      </x:c>
+      <x:c r="J54" s="34" t="str">
+        <x:v>年鉴现价值；优选</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="16" t="str">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="B55" s="6" t="str">
+        <x:v>gdp</x:v>
+      </x:c>
+      <x:c r="C55" s="18" t="str">
+        <x:v>311.94</x:v>
+      </x:c>
+      <x:c r="D55" s="6" t="str">
+        <x:v>100m_cny</x:v>
+      </x:c>
+      <x:c r="E55" s="24" t="str">
+        <x:v>official_initial</x:v>
+      </x:c>
+      <x:c r="F55" s="24" t="str">
+        <x:v>2025_statistical_bulletin</x:v>
+      </x:c>
+      <x:c r="G55" s="6" t="str">
+        <x:v>gov_jz_bulletin_2025</x:v>
+      </x:c>
+      <x:c r="H55" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I55" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202606/t20260629_7325623.html</x:v>
+      </x:c>
+      <x:c r="J55" s="34" t="str"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="16" t="str">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="B56" s="6" t="str">
+        <x:v>tertiary_value_added</x:v>
+      </x:c>
+      <x:c r="C56" s="18" t="str">
         <x:v>195.17</x:v>
       </x:c>
-      <x:c r="D38" s="6" t="str">
-        <x:v>100m_cny</x:v>
-      </x:c>
-      <x:c r="E38" s="24" t="str">
+      <x:c r="D56" s="6" t="str">
+        <x:v>100m_cny</x:v>
+      </x:c>
+      <x:c r="E56" s="24" t="str">
         <x:v>official_initial</x:v>
       </x:c>
-      <x:c r="F38" s="24" t="str">
+      <x:c r="F56" s="24" t="str">
         <x:v>2025_statistical_bulletin</x:v>
       </x:c>
-      <x:c r="G38" s="6" t="str">
+      <x:c r="G56" s="6" t="str">
         <x:v>gov_jz_bulletin_2025</x:v>
       </x:c>
-      <x:c r="H38" s="36" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I38" s="34" t="str">
+      <x:c r="H56" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I56" s="34" t="str">
         <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202606/t20260629_7325623.html</x:v>
       </x:c>
-      <x:c r="J38" s="34" t="str"/>
+      <x:c r="J56" s="34" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5080,40 +5688,42 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="16" t="str">
-        <x:v>2021</x:v>
+        <x:v>2020</x:v>
       </x:c>
       <x:c r="B21" s="6" t="str">
-        <x:v>all_resident_disposable_income</x:v>
+        <x:v>road_mileage</x:v>
       </x:c>
       <x:c r="C21" s="18" t="str">
-        <x:v>32008</x:v>
+        <x:v>3076</x:v>
       </x:c>
       <x:c r="D21" s="6" t="str">
-        <x:v>cny_per_person</x:v>
+        <x:v>km</x:v>
       </x:c>
       <x:c r="E21" s="24" t="str">
         <x:v>observed</x:v>
       </x:c>
       <x:c r="F21" s="6" t="str">
-        <x:v>gov_jz_bulletin_2021</x:v>
+        <x:v>gov_jz_bulletin_2020</x:v>
       </x:c>
       <x:c r="G21" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202211/t20221128_6044247.html</x:v>
-      </x:c>
-      <x:c r="H21" s="34" t="str"/>
+        <x:v>https://www.tjjz.gov.cn/zwgk/zfxxgkqjjg/tjj1/fdzdgknr34/tjxx34/202111/t20211115_5703949.html</x:v>
+      </x:c>
+      <x:c r="H21" s="34" t="str">
+        <x:v>全区境内通车总里程；按公报原值录入</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="16" t="str">
         <x:v>2021</x:v>
       </x:c>
       <x:c r="B22" s="6" t="str">
-        <x:v>social_retail_sales</x:v>
+        <x:v>all_resident_disposable_income</x:v>
       </x:c>
       <x:c r="C22" s="18" t="str">
-        <x:v>55.45</x:v>
+        <x:v>32008</x:v>
       </x:c>
       <x:c r="D22" s="6" t="str">
-        <x:v>100m_cny</x:v>
+        <x:v>cny_per_person</x:v>
       </x:c>
       <x:c r="E22" s="24" t="str">
         <x:v>observed</x:v>
@@ -5124,19 +5734,17 @@
       <x:c r="G22" s="34" t="str">
         <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202211/t20221128_6044247.html</x:v>
       </x:c>
-      <x:c r="H22" s="34" t="str">
-        <x:v>与2017年前旧统计表存在范围断点</x:v>
-      </x:c>
+      <x:c r="H22" s="34" t="str"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="16" t="str">
         <x:v>2021</x:v>
       </x:c>
       <x:c r="B23" s="6" t="str">
-        <x:v>general_public_budget_expenditure</x:v>
+        <x:v>social_retail_sales</x:v>
       </x:c>
       <x:c r="C23" s="18" t="str">
-        <x:v>115.12</x:v>
+        <x:v>55.45</x:v>
       </x:c>
       <x:c r="D23" s="6" t="str">
         <x:v>100m_cny</x:v>
@@ -5150,139 +5758,143 @@
       <x:c r="G23" s="34" t="str">
         <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202211/t20221128_6044247.html</x:v>
       </x:c>
-      <x:c r="H23" s="34" t="str"/>
+      <x:c r="H23" s="34" t="str">
+        <x:v>与2017年前旧统计表存在范围断点</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="16" t="str">
-        <x:v>2022</x:v>
+        <x:v>2021</x:v>
       </x:c>
       <x:c r="B24" s="6" t="str">
-        <x:v>all_resident_disposable_income</x:v>
+        <x:v>general_public_budget_expenditure</x:v>
       </x:c>
       <x:c r="C24" s="18" t="str">
-        <x:v>33073</x:v>
+        <x:v>115.12</x:v>
       </x:c>
       <x:c r="D24" s="6" t="str">
-        <x:v>cny_per_person</x:v>
+        <x:v>100m_cny</x:v>
       </x:c>
       <x:c r="E24" s="24" t="str">
         <x:v>observed</x:v>
       </x:c>
       <x:c r="F24" s="6" t="str">
-        <x:v>gov_jz_bulletin_2022</x:v>
+        <x:v>gov_jz_bulletin_2021</x:v>
       </x:c>
       <x:c r="G24" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202311/t20231107_6450006.html</x:v>
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202211/t20221128_6044247.html</x:v>
       </x:c>
       <x:c r="H24" s="34" t="str"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="16" t="str">
-        <x:v>2022</x:v>
+        <x:v>2021</x:v>
       </x:c>
       <x:c r="B25" s="6" t="str">
-        <x:v>social_retail_sales</x:v>
+        <x:v>culture_tourism_sports_media_expenditure</x:v>
       </x:c>
       <x:c r="C25" s="18" t="str">
-        <x:v>55.58</x:v>
+        <x:v>9979</x:v>
       </x:c>
       <x:c r="D25" s="6" t="str">
-        <x:v>100m_cny</x:v>
+        <x:v>10k_cny</x:v>
       </x:c>
       <x:c r="E25" s="24" t="str">
         <x:v>observed</x:v>
       </x:c>
       <x:c r="F25" s="6" t="str">
-        <x:v>gov_jz_bulletin_2022</x:v>
+        <x:v>gov_jz_yearbook_2021</x:v>
       </x:c>
       <x:c r="G25" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202311/t20231107_6450006.html</x:v>
-      </x:c>
-      <x:c r="H25" s="34" t="str"/>
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202211/W020250107625770490134.rar</x:v>
+      </x:c>
+      <x:c r="H25" s="34" t="str">
+        <x:v>财政功能分类支出；并非全部旅游专项投入</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="16" t="str">
-        <x:v>2022</x:v>
+        <x:v>2021</x:v>
       </x:c>
       <x:c r="B26" s="6" t="str">
-        <x:v>general_public_budget_expenditure</x:v>
+        <x:v>road_mileage</x:v>
       </x:c>
       <x:c r="C26" s="18" t="str">
-        <x:v>92.8</x:v>
+        <x:v>3084</x:v>
       </x:c>
       <x:c r="D26" s="6" t="str">
-        <x:v>100m_cny</x:v>
+        <x:v>km</x:v>
       </x:c>
       <x:c r="E26" s="24" t="str">
         <x:v>observed</x:v>
       </x:c>
       <x:c r="F26" s="6" t="str">
-        <x:v>gov_jz_bulletin_2022</x:v>
+        <x:v>gov_jz_bulletin_2021</x:v>
       </x:c>
       <x:c r="G26" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202311/t20231107_6450006.html</x:v>
-      </x:c>
-      <x:c r="H26" s="34" t="str"/>
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202211/t20221128_6044247.html</x:v>
+      </x:c>
+      <x:c r="H26" s="34" t="str">
+        <x:v>全区境内通车总里程；按公报原值录入</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="16" t="str">
         <x:v>2022</x:v>
       </x:c>
       <x:c r="B27" s="6" t="str">
-        <x:v>culture_tourism_sports_media_expenditure</x:v>
+        <x:v>all_resident_disposable_income</x:v>
       </x:c>
       <x:c r="C27" s="18" t="str">
-        <x:v>7445</x:v>
+        <x:v>33073</x:v>
       </x:c>
       <x:c r="D27" s="6" t="str">
-        <x:v>10k_cny</x:v>
+        <x:v>cny_per_person</x:v>
       </x:c>
       <x:c r="E27" s="24" t="str">
         <x:v>observed</x:v>
       </x:c>
       <x:c r="F27" s="6" t="str">
-        <x:v>gov_jz_yearbook_2022</x:v>
+        <x:v>gov_jz_bulletin_2022</x:v>
       </x:c>
       <x:c r="G27" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202311/W020250107625663560312.pdf</x:v>
-      </x:c>
-      <x:c r="H27" s="34" t="str">
-        <x:v>财政功能分类支出；并非全部旅游专项投入</x:v>
-      </x:c>
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202311/t20231107_6450006.html</x:v>
+      </x:c>
+      <x:c r="H27" s="34" t="str"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="16" t="str">
-        <x:v>2023</x:v>
+        <x:v>2022</x:v>
       </x:c>
       <x:c r="B28" s="6" t="str">
-        <x:v>all_resident_disposable_income</x:v>
+        <x:v>social_retail_sales</x:v>
       </x:c>
       <x:c r="C28" s="18" t="str">
-        <x:v>35116</x:v>
+        <x:v>55.58</x:v>
       </x:c>
       <x:c r="D28" s="6" t="str">
-        <x:v>cny_per_person</x:v>
+        <x:v>100m_cny</x:v>
       </x:c>
       <x:c r="E28" s="24" t="str">
         <x:v>observed</x:v>
       </x:c>
       <x:c r="F28" s="6" t="str">
-        <x:v>gov_jz_bulletin_2023</x:v>
+        <x:v>gov_jz_bulletin_2022</x:v>
       </x:c>
       <x:c r="G28" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/zfxxgkqjjg/tjj1/fdzdgknr34/tjxx34/202406/t20240627_6662772.html</x:v>
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202311/t20231107_6450006.html</x:v>
       </x:c>
       <x:c r="H28" s="34" t="str"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="16" t="str">
-        <x:v>2023</x:v>
+        <x:v>2022</x:v>
       </x:c>
       <x:c r="B29" s="6" t="str">
-        <x:v>social_retail_sales</x:v>
+        <x:v>general_public_budget_expenditure</x:v>
       </x:c>
       <x:c r="C29" s="18" t="str">
-        <x:v>57.71</x:v>
+        <x:v>92.8</x:v>
       </x:c>
       <x:c r="D29" s="6" t="str">
         <x:v>100m_cny</x:v>
@@ -5291,72 +5903,74 @@
         <x:v>observed</x:v>
       </x:c>
       <x:c r="F29" s="6" t="str">
-        <x:v>gov_jz_bulletin_2023</x:v>
+        <x:v>gov_jz_bulletin_2022</x:v>
       </x:c>
       <x:c r="G29" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/zfxxgkqjjg/tjj1/fdzdgknr34/tjxx34/202406/t20240627_6662772.html</x:v>
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202311/t20231107_6450006.html</x:v>
       </x:c>
       <x:c r="H29" s="34" t="str"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="16" t="str">
-        <x:v>2023</x:v>
+        <x:v>2022</x:v>
       </x:c>
       <x:c r="B30" s="6" t="str">
-        <x:v>general_public_budget_expenditure</x:v>
+        <x:v>culture_tourism_sports_media_expenditure</x:v>
       </x:c>
       <x:c r="C30" s="18" t="str">
-        <x:v>78.89</x:v>
+        <x:v>7445</x:v>
       </x:c>
       <x:c r="D30" s="6" t="str">
-        <x:v>100m_cny</x:v>
+        <x:v>10k_cny</x:v>
       </x:c>
       <x:c r="E30" s="24" t="str">
         <x:v>observed</x:v>
       </x:c>
       <x:c r="F30" s="6" t="str">
-        <x:v>gov_jz_bulletin_2023</x:v>
+        <x:v>gov_jz_yearbook_2022</x:v>
       </x:c>
       <x:c r="G30" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/zfxxgkqjjg/tjj1/fdzdgknr34/tjxx34/202406/t20240627_6662772.html</x:v>
-      </x:c>
-      <x:c r="H30" s="34" t="str"/>
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202311/W020250107625663560312.pdf</x:v>
+      </x:c>
+      <x:c r="H30" s="34" t="str">
+        <x:v>财政功能分类支出；并非全部旅游专项投入</x:v>
+      </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="16" t="str">
-        <x:v>2023</x:v>
+        <x:v>2022</x:v>
       </x:c>
       <x:c r="B31" s="6" t="str">
-        <x:v>culture_tourism_sports_media_expenditure</x:v>
+        <x:v>road_mileage</x:v>
       </x:c>
       <x:c r="C31" s="18" t="str">
-        <x:v>5677</x:v>
+        <x:v>3071</x:v>
       </x:c>
       <x:c r="D31" s="6" t="str">
-        <x:v>10k_cny</x:v>
+        <x:v>km</x:v>
       </x:c>
       <x:c r="E31" s="24" t="str">
         <x:v>observed</x:v>
       </x:c>
       <x:c r="F31" s="6" t="str">
-        <x:v>gov_jz_yearbook_2023</x:v>
+        <x:v>gov_jz_bulletin_2022</x:v>
       </x:c>
       <x:c r="G31" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202501/W020250103638170510358.pdf</x:v>
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202311/t20231107_6450006.html</x:v>
       </x:c>
       <x:c r="H31" s="34" t="str">
-        <x:v>财政功能分类支出；并非全部旅游专项投入</x:v>
+        <x:v>全区境内通车总里程；按公报原值录入</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="16" t="str">
-        <x:v>2024</x:v>
+        <x:v>2023</x:v>
       </x:c>
       <x:c r="B32" s="6" t="str">
         <x:v>all_resident_disposable_income</x:v>
       </x:c>
       <x:c r="C32" s="18" t="str">
-        <x:v>36998</x:v>
+        <x:v>35116</x:v>
       </x:c>
       <x:c r="D32" s="6" t="str">
         <x:v>cny_per_person</x:v>
@@ -5365,22 +5979,22 @@
         <x:v>observed</x:v>
       </x:c>
       <x:c r="F32" s="6" t="str">
-        <x:v>gov_jz_bulletin_2024</x:v>
+        <x:v>gov_jz_bulletin_2023</x:v>
       </x:c>
       <x:c r="G32" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202506/t20250630_6969506.html</x:v>
+        <x:v>https://www.tjjz.gov.cn/zwgk/zfxxgkqjjg/tjj1/fdzdgknr34/tjxx34/202406/t20240627_6662772.html</x:v>
       </x:c>
       <x:c r="H32" s="34" t="str"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="16" t="str">
-        <x:v>2024</x:v>
+        <x:v>2023</x:v>
       </x:c>
       <x:c r="B33" s="6" t="str">
         <x:v>social_retail_sales</x:v>
       </x:c>
       <x:c r="C33" s="18" t="str">
-        <x:v>58.88</x:v>
+        <x:v>57.71</x:v>
       </x:c>
       <x:c r="D33" s="6" t="str">
         <x:v>100m_cny</x:v>
@@ -5389,22 +6003,22 @@
         <x:v>observed</x:v>
       </x:c>
       <x:c r="F33" s="6" t="str">
-        <x:v>gov_jz_bulletin_2024</x:v>
+        <x:v>gov_jz_bulletin_2023</x:v>
       </x:c>
       <x:c r="G33" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202506/t20250630_6969506.html</x:v>
+        <x:v>https://www.tjjz.gov.cn/zwgk/zfxxgkqjjg/tjj1/fdzdgknr34/tjxx34/202406/t20240627_6662772.html</x:v>
       </x:c>
       <x:c r="H33" s="34" t="str"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="16" t="str">
-        <x:v>2024</x:v>
+        <x:v>2023</x:v>
       </x:c>
       <x:c r="B34" s="6" t="str">
         <x:v>general_public_budget_expenditure</x:v>
       </x:c>
       <x:c r="C34" s="18" t="str">
-        <x:v>74.2</x:v>
+        <x:v>78.89</x:v>
       </x:c>
       <x:c r="D34" s="6" t="str">
         <x:v>100m_cny</x:v>
@@ -5413,22 +6027,22 @@
         <x:v>observed</x:v>
       </x:c>
       <x:c r="F34" s="6" t="str">
-        <x:v>gov_jz_bulletin_2024</x:v>
+        <x:v>gov_jz_bulletin_2023</x:v>
       </x:c>
       <x:c r="G34" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202506/t20250630_6969506.html</x:v>
+        <x:v>https://www.tjjz.gov.cn/zwgk/zfxxgkqjjg/tjj1/fdzdgknr34/tjxx34/202406/t20240627_6662772.html</x:v>
       </x:c>
       <x:c r="H34" s="34" t="str"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="16" t="str">
-        <x:v>2024</x:v>
+        <x:v>2023</x:v>
       </x:c>
       <x:c r="B35" s="6" t="str">
         <x:v>culture_tourism_sports_media_expenditure</x:v>
       </x:c>
       <x:c r="C35" s="18" t="str">
-        <x:v>5110</x:v>
+        <x:v>5677</x:v>
       </x:c>
       <x:c r="D35" s="6" t="str">
         <x:v>10k_cny</x:v>
@@ -5437,10 +6051,10 @@
         <x:v>observed</x:v>
       </x:c>
       <x:c r="F35" s="6" t="str">
-        <x:v>gov_jz_yearbook_2024</x:v>
+        <x:v>gov_jz_yearbook_2023</x:v>
       </x:c>
       <x:c r="G35" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202511/W020251126560102082891.pdf</x:v>
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202501/W020250103638170510358.pdf</x:v>
       </x:c>
       <x:c r="H35" s="34" t="str">
         <x:v>财政功能分类支出；并非全部旅游专项投入</x:v>
@@ -5448,63 +6062,63 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="16" t="str">
-        <x:v>2025</x:v>
+        <x:v>2023</x:v>
       </x:c>
       <x:c r="B36" s="6" t="str">
-        <x:v>all_resident_disposable_income</x:v>
+        <x:v>road_mileage</x:v>
       </x:c>
       <x:c r="C36" s="18" t="str">
-        <x:v>38617</x:v>
+        <x:v>3071</x:v>
       </x:c>
       <x:c r="D36" s="6" t="str">
-        <x:v>cny_per_person</x:v>
+        <x:v>km</x:v>
       </x:c>
       <x:c r="E36" s="24" t="str">
         <x:v>observed</x:v>
       </x:c>
       <x:c r="F36" s="6" t="str">
-        <x:v>gov_jz_bulletin_2025</x:v>
+        <x:v>gov_jz_bulletin_2023</x:v>
       </x:c>
       <x:c r="G36" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202606/t20260629_7325623.html</x:v>
-      </x:c>
-      <x:c r="H36" s="34" t="str"/>
+        <x:v>https://www.tjjz.gov.cn/zwgk/zfxxgkqjjg/tjj1/fdzdgknr34/tjxx34/202406/t20240627_6662772.html</x:v>
+      </x:c>
+      <x:c r="H36" s="34" t="str">
+        <x:v>全区境内通车总里程；按公报原值录入</x:v>
+      </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="16" t="str">
-        <x:v>2025</x:v>
+        <x:v>2024</x:v>
       </x:c>
       <x:c r="B37" s="6" t="str">
-        <x:v>social_retail_sales</x:v>
+        <x:v>all_resident_disposable_income</x:v>
       </x:c>
       <x:c r="C37" s="18" t="str">
-        <x:v>75.58</x:v>
+        <x:v>36998</x:v>
       </x:c>
       <x:c r="D37" s="6" t="str">
-        <x:v>100m_cny</x:v>
+        <x:v>cny_per_person</x:v>
       </x:c>
       <x:c r="E37" s="24" t="str">
         <x:v>observed</x:v>
       </x:c>
       <x:c r="F37" s="6" t="str">
-        <x:v>gov_jz_bulletin_2025</x:v>
+        <x:v>gov_jz_bulletin_2024</x:v>
       </x:c>
       <x:c r="G37" s="34" t="str">
-        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202606/t20260629_7325623.html</x:v>
-      </x:c>
-      <x:c r="H37" s="34" t="str">
-        <x:v>与2024年同比口径存在需进一步核验的水平跃升</x:v>
-      </x:c>
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202506/t20250630_6969506.html</x:v>
+      </x:c>
+      <x:c r="H37" s="34" t="str"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="16" t="str">
-        <x:v>2025</x:v>
+        <x:v>2024</x:v>
       </x:c>
       <x:c r="B38" s="6" t="str">
-        <x:v>general_public_budget_expenditure</x:v>
+        <x:v>social_retail_sales</x:v>
       </x:c>
       <x:c r="C38" s="18" t="str">
-        <x:v>83.76</x:v>
+        <x:v>58.88</x:v>
       </x:c>
       <x:c r="D38" s="6" t="str">
         <x:v>100m_cny</x:v>
@@ -5513,12 +6127,188 @@
         <x:v>observed</x:v>
       </x:c>
       <x:c r="F38" s="6" t="str">
+        <x:v>gov_jz_bulletin_2024</x:v>
+      </x:c>
+      <x:c r="G38" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202506/t20250630_6969506.html</x:v>
+      </x:c>
+      <x:c r="H38" s="34" t="str"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="16" t="str">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B39" s="6" t="str">
+        <x:v>general_public_budget_expenditure</x:v>
+      </x:c>
+      <x:c r="C39" s="18" t="str">
+        <x:v>74.2</x:v>
+      </x:c>
+      <x:c r="D39" s="6" t="str">
+        <x:v>100m_cny</x:v>
+      </x:c>
+      <x:c r="E39" s="24" t="str">
+        <x:v>observed</x:v>
+      </x:c>
+      <x:c r="F39" s="6" t="str">
+        <x:v>gov_jz_bulletin_2024</x:v>
+      </x:c>
+      <x:c r="G39" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202506/t20250630_6969506.html</x:v>
+      </x:c>
+      <x:c r="H39" s="34" t="str"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="16" t="str">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B40" s="6" t="str">
+        <x:v>culture_tourism_sports_media_expenditure</x:v>
+      </x:c>
+      <x:c r="C40" s="18" t="str">
+        <x:v>5110</x:v>
+      </x:c>
+      <x:c r="D40" s="6" t="str">
+        <x:v>10k_cny</x:v>
+      </x:c>
+      <x:c r="E40" s="24" t="str">
+        <x:v>observed</x:v>
+      </x:c>
+      <x:c r="F40" s="6" t="str">
+        <x:v>gov_jz_yearbook_2024</x:v>
+      </x:c>
+      <x:c r="G40" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202511/W020251126560102082891.pdf</x:v>
+      </x:c>
+      <x:c r="H40" s="34" t="str">
+        <x:v>财政功能分类支出；并非全部旅游专项投入</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="16" t="str">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B41" s="6" t="str">
+        <x:v>road_mileage</x:v>
+      </x:c>
+      <x:c r="C41" s="18" t="str">
+        <x:v>3073</x:v>
+      </x:c>
+      <x:c r="D41" s="6" t="str">
+        <x:v>km</x:v>
+      </x:c>
+      <x:c r="E41" s="24" t="str">
+        <x:v>observed</x:v>
+      </x:c>
+      <x:c r="F41" s="6" t="str">
+        <x:v>gov_jz_bulletin_2024</x:v>
+      </x:c>
+      <x:c r="G41" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202506/t20250630_6969506.html</x:v>
+      </x:c>
+      <x:c r="H41" s="34" t="str">
+        <x:v>全区境内通车总里程；按公报原值录入</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="16" t="str">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="B42" s="6" t="str">
+        <x:v>all_resident_disposable_income</x:v>
+      </x:c>
+      <x:c r="C42" s="18" t="str">
+        <x:v>38617</x:v>
+      </x:c>
+      <x:c r="D42" s="6" t="str">
+        <x:v>cny_per_person</x:v>
+      </x:c>
+      <x:c r="E42" s="24" t="str">
+        <x:v>observed</x:v>
+      </x:c>
+      <x:c r="F42" s="6" t="str">
         <x:v>gov_jz_bulletin_2025</x:v>
       </x:c>
-      <x:c r="G38" s="34" t="str">
+      <x:c r="G42" s="34" t="str">
         <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202606/t20260629_7325623.html</x:v>
       </x:c>
-      <x:c r="H38" s="34" t="str"/>
+      <x:c r="H42" s="34" t="str"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="16" t="str">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="B43" s="6" t="str">
+        <x:v>social_retail_sales</x:v>
+      </x:c>
+      <x:c r="C43" s="18" t="str">
+        <x:v>75.58</x:v>
+      </x:c>
+      <x:c r="D43" s="6" t="str">
+        <x:v>100m_cny</x:v>
+      </x:c>
+      <x:c r="E43" s="24" t="str">
+        <x:v>observed</x:v>
+      </x:c>
+      <x:c r="F43" s="6" t="str">
+        <x:v>gov_jz_bulletin_2025</x:v>
+      </x:c>
+      <x:c r="G43" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202606/t20260629_7325623.html</x:v>
+      </x:c>
+      <x:c r="H43" s="34" t="str">
+        <x:v>与2024年同比口径存在需进一步核验的水平跃升</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="16" t="str">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="B44" s="6" t="str">
+        <x:v>general_public_budget_expenditure</x:v>
+      </x:c>
+      <x:c r="C44" s="18" t="str">
+        <x:v>83.76</x:v>
+      </x:c>
+      <x:c r="D44" s="6" t="str">
+        <x:v>100m_cny</x:v>
+      </x:c>
+      <x:c r="E44" s="24" t="str">
+        <x:v>observed</x:v>
+      </x:c>
+      <x:c r="F44" s="6" t="str">
+        <x:v>gov_jz_bulletin_2025</x:v>
+      </x:c>
+      <x:c r="G44" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202606/t20260629_7325623.html</x:v>
+      </x:c>
+      <x:c r="H44" s="34" t="str"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="16" t="str">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="B45" s="6" t="str">
+        <x:v>road_mileage</x:v>
+      </x:c>
+      <x:c r="C45" s="18" t="str">
+        <x:v>3071.683</x:v>
+      </x:c>
+      <x:c r="D45" s="6" t="str">
+        <x:v>km</x:v>
+      </x:c>
+      <x:c r="E45" s="24" t="str">
+        <x:v>observed</x:v>
+      </x:c>
+      <x:c r="F45" s="6" t="str">
+        <x:v>gov_jz_bulletin_2025</x:v>
+      </x:c>
+      <x:c r="G45" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjgb/202606/t20260629_7325623.html</x:v>
+      </x:c>
+      <x:c r="H45" s="34" t="str">
+        <x:v>全区境内通车总里程；保留公报三位小数原精度</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5526,6 +6316,1798 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="43" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="27" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="31" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="11" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="66" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="58" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="14" t="str">
+        <x:v>年份</x:v>
+      </x:c>
+      <x:c r="B1" s="14" t="str">
+        <x:v>指标</x:v>
+      </x:c>
+      <x:c r="C1" s="14" t="str">
+        <x:v>数值</x:v>
+      </x:c>
+      <x:c r="D1" s="14" t="str">
+        <x:v>单位</x:v>
+      </x:c>
+      <x:c r="E1" s="14" t="str">
+        <x:v>值状态</x:v>
+      </x:c>
+      <x:c r="F1" s="14" t="str">
+        <x:v>指标范围</x:v>
+      </x:c>
+      <x:c r="G1" s="14" t="str">
+        <x:v>版本</x:v>
+      </x:c>
+      <x:c r="H1" s="14" t="str">
+        <x:v>来源ID</x:v>
+      </x:c>
+      <x:c r="I1" s="14" t="str">
+        <x:v>证据等级</x:v>
+      </x:c>
+      <x:c r="J1" s="14" t="str">
+        <x:v>来源URL</x:v>
+      </x:c>
+      <x:c r="K1" s="14" t="str">
+        <x:v>备注</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="16" t="str">
+        <x:v>2012</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="str">
+        <x:v>guest_rooms</x:v>
+      </x:c>
+      <x:c r="C2" s="18" t="str">
+        <x:v>2587</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="E2" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F2" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G2" s="24" t="str">
+        <x:v>jizhou_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="H2" s="6" t="str">
+        <x:v>gov_jz_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="I2" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J2" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202211/W020250107625770490134.rar</x:v>
+      </x:c>
+      <x:c r="K2" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="16" t="str">
+        <x:v>2012</x:v>
+      </x:c>
+      <x:c r="B3" s="6" t="str">
+        <x:v>beds</x:v>
+      </x:c>
+      <x:c r="C3" s="18" t="str">
+        <x:v>5248</x:v>
+      </x:c>
+      <x:c r="D3" s="6" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="E3" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F3" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G3" s="24" t="str">
+        <x:v>jizhou_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="H3" s="6" t="str">
+        <x:v>gov_jz_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="I3" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J3" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202211/W020250107625770490134.rar</x:v>
+      </x:c>
+      <x:c r="K3" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="16" t="str">
+        <x:v>2012</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="str">
+        <x:v>room_revenue</x:v>
+      </x:c>
+      <x:c r="C4" s="18" t="str">
+        <x:v>8462.8</x:v>
+      </x:c>
+      <x:c r="D4" s="6" t="str">
+        <x:v>10k_cny</x:v>
+      </x:c>
+      <x:c r="E4" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F4" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G4" s="24" t="str">
+        <x:v>jizhou_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="H4" s="6" t="str">
+        <x:v>gov_jz_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="I4" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J4" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202211/W020250107625770490134.rar</x:v>
+      </x:c>
+      <x:c r="K4" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="16" t="str">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="str">
+        <x:v>guest_rooms</x:v>
+      </x:c>
+      <x:c r="C5" s="18" t="str">
+        <x:v>3624</x:v>
+      </x:c>
+      <x:c r="D5" s="6" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="E5" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F5" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G5" s="24" t="str">
+        <x:v>jizhou_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="H5" s="6" t="str">
+        <x:v>gov_jz_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="I5" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J5" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202211/W020250107625770490134.rar</x:v>
+      </x:c>
+      <x:c r="K5" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="16" t="str">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="str">
+        <x:v>beds</x:v>
+      </x:c>
+      <x:c r="C6" s="18" t="str">
+        <x:v>7350</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="E6" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F6" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G6" s="24" t="str">
+        <x:v>jizhou_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="H6" s="6" t="str">
+        <x:v>gov_jz_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="I6" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J6" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202211/W020250107625770490134.rar</x:v>
+      </x:c>
+      <x:c r="K6" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="16" t="str">
+        <x:v>2013</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="str">
+        <x:v>room_revenue</x:v>
+      </x:c>
+      <x:c r="C7" s="18" t="str">
+        <x:v>12247</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="str">
+        <x:v>10k_cny</x:v>
+      </x:c>
+      <x:c r="E7" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F7" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G7" s="24" t="str">
+        <x:v>jizhou_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="H7" s="6" t="str">
+        <x:v>gov_jz_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="I7" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J7" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202211/W020250107625770490134.rar</x:v>
+      </x:c>
+      <x:c r="K7" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="16" t="str">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="str">
+        <x:v>guest_rooms</x:v>
+      </x:c>
+      <x:c r="C8" s="18" t="str">
+        <x:v>3739</x:v>
+      </x:c>
+      <x:c r="D8" s="6" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="E8" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F8" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G8" s="24" t="str">
+        <x:v>jizhou_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="H8" s="6" t="str">
+        <x:v>gov_jz_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="I8" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J8" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202211/W020250107625770490134.rar</x:v>
+      </x:c>
+      <x:c r="K8" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="16" t="str">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="str">
+        <x:v>beds</x:v>
+      </x:c>
+      <x:c r="C9" s="18" t="str">
+        <x:v>7589</x:v>
+      </x:c>
+      <x:c r="D9" s="6" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="E9" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F9" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G9" s="24" t="str">
+        <x:v>jizhou_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="H9" s="6" t="str">
+        <x:v>gov_jz_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="I9" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J9" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202211/W020250107625770490134.rar</x:v>
+      </x:c>
+      <x:c r="K9" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="16" t="str">
+        <x:v>2014</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="str">
+        <x:v>room_revenue</x:v>
+      </x:c>
+      <x:c r="C10" s="18" t="str">
+        <x:v>9777.6</x:v>
+      </x:c>
+      <x:c r="D10" s="6" t="str">
+        <x:v>10k_cny</x:v>
+      </x:c>
+      <x:c r="E10" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F10" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G10" s="24" t="str">
+        <x:v>jizhou_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="H10" s="6" t="str">
+        <x:v>gov_jz_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="I10" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J10" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202211/W020250107625770490134.rar</x:v>
+      </x:c>
+      <x:c r="K10" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="16" t="str">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="str">
+        <x:v>guest_rooms</x:v>
+      </x:c>
+      <x:c r="C11" s="18" t="str">
+        <x:v>4008</x:v>
+      </x:c>
+      <x:c r="D11" s="6" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="E11" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F11" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G11" s="24" t="str">
+        <x:v>jizhou_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="H11" s="6" t="str">
+        <x:v>gov_jz_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="I11" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J11" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202211/W020250107625770490134.rar</x:v>
+      </x:c>
+      <x:c r="K11" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="16" t="str">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="str">
+        <x:v>beds</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="str">
+        <x:v>7936</x:v>
+      </x:c>
+      <x:c r="D12" s="6" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="E12" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F12" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G12" s="24" t="str">
+        <x:v>jizhou_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="H12" s="6" t="str">
+        <x:v>gov_jz_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="I12" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J12" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202211/W020250107625770490134.rar</x:v>
+      </x:c>
+      <x:c r="K12" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="16" t="str">
+        <x:v>2015</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="str">
+        <x:v>room_revenue</x:v>
+      </x:c>
+      <x:c r="C13" s="18" t="str">
+        <x:v>12642.8</x:v>
+      </x:c>
+      <x:c r="D13" s="6" t="str">
+        <x:v>10k_cny</x:v>
+      </x:c>
+      <x:c r="E13" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F13" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G13" s="24" t="str">
+        <x:v>jizhou_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="H13" s="6" t="str">
+        <x:v>gov_jz_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="I13" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J13" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202211/W020250107625770490134.rar</x:v>
+      </x:c>
+      <x:c r="K13" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="16" t="str">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="B14" s="6" t="str">
+        <x:v>guest_rooms</x:v>
+      </x:c>
+      <x:c r="C14" s="18" t="str">
+        <x:v>6744</x:v>
+      </x:c>
+      <x:c r="D14" s="6" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="E14" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F14" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G14" s="24" t="str">
+        <x:v>jizhou_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="H14" s="6" t="str">
+        <x:v>gov_jz_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="I14" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J14" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202211/W020250107625770490134.rar</x:v>
+      </x:c>
+      <x:c r="K14" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；2016—2017存在明显名录或范围断点</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="16" t="str">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="B15" s="6" t="str">
+        <x:v>beds</x:v>
+      </x:c>
+      <x:c r="C15" s="18" t="str">
+        <x:v>16386</x:v>
+      </x:c>
+      <x:c r="D15" s="6" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="E15" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F15" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G15" s="24" t="str">
+        <x:v>jizhou_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="H15" s="6" t="str">
+        <x:v>gov_jz_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="I15" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J15" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202211/W020250107625770490134.rar</x:v>
+      </x:c>
+      <x:c r="K15" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；2016—2017存在明显名录或范围断点</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="16" t="str">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="B16" s="6" t="str">
+        <x:v>room_revenue</x:v>
+      </x:c>
+      <x:c r="C16" s="18" t="str">
+        <x:v>12261.3</x:v>
+      </x:c>
+      <x:c r="D16" s="6" t="str">
+        <x:v>10k_cny</x:v>
+      </x:c>
+      <x:c r="E16" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F16" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G16" s="24" t="str">
+        <x:v>jizhou_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="H16" s="6" t="str">
+        <x:v>gov_jz_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="I16" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J16" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202211/W020250107625770490134.rar</x:v>
+      </x:c>
+      <x:c r="K16" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；2016—2017存在明显名录或范围断点</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="16" t="str">
+        <x:v>2017</x:v>
+      </x:c>
+      <x:c r="B17" s="6" t="str">
+        <x:v>guest_rooms</x:v>
+      </x:c>
+      <x:c r="C17" s="18" t="str">
+        <x:v>1402</x:v>
+      </x:c>
+      <x:c r="D17" s="6" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="E17" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F17" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G17" s="24" t="str">
+        <x:v>jizhou_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="H17" s="6" t="str">
+        <x:v>gov_jz_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="I17" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J17" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202211/W020250107625770490134.rar</x:v>
+      </x:c>
+      <x:c r="K17" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；2016—2017存在明显名录或范围断点</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="16" t="str">
+        <x:v>2017</x:v>
+      </x:c>
+      <x:c r="B18" s="6" t="str">
+        <x:v>beds</x:v>
+      </x:c>
+      <x:c r="C18" s="18" t="str">
+        <x:v>2772</x:v>
+      </x:c>
+      <x:c r="D18" s="6" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="E18" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F18" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G18" s="24" t="str">
+        <x:v>jizhou_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="H18" s="6" t="str">
+        <x:v>gov_jz_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="I18" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J18" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202211/W020250107625770490134.rar</x:v>
+      </x:c>
+      <x:c r="K18" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；2016—2017存在明显名录或范围断点</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="16" t="str">
+        <x:v>2017</x:v>
+      </x:c>
+      <x:c r="B19" s="6" t="str">
+        <x:v>room_revenue</x:v>
+      </x:c>
+      <x:c r="C19" s="18" t="str">
+        <x:v>5855</x:v>
+      </x:c>
+      <x:c r="D19" s="6" t="str">
+        <x:v>10k_cny</x:v>
+      </x:c>
+      <x:c r="E19" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F19" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G19" s="24" t="str">
+        <x:v>jizhou_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="H19" s="6" t="str">
+        <x:v>gov_jz_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="I19" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J19" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202211/W020250107625770490134.rar</x:v>
+      </x:c>
+      <x:c r="K19" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；2016—2017存在明显名录或范围断点</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="16" t="str">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="B20" s="6" t="str">
+        <x:v>guest_rooms</x:v>
+      </x:c>
+      <x:c r="C20" s="18" t="str">
+        <x:v>1402</x:v>
+      </x:c>
+      <x:c r="D20" s="6" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="E20" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F20" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G20" s="24" t="str">
+        <x:v>jizhou_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="H20" s="6" t="str">
+        <x:v>gov_jz_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="I20" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J20" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202211/W020250107625770490134.rar</x:v>
+      </x:c>
+      <x:c r="K20" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="16" t="str">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="B21" s="6" t="str">
+        <x:v>beds</x:v>
+      </x:c>
+      <x:c r="C21" s="18" t="str">
+        <x:v>2596</x:v>
+      </x:c>
+      <x:c r="D21" s="6" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="E21" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F21" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G21" s="24" t="str">
+        <x:v>jizhou_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="H21" s="6" t="str">
+        <x:v>gov_jz_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="I21" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J21" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202211/W020250107625770490134.rar</x:v>
+      </x:c>
+      <x:c r="K21" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="16" t="str">
+        <x:v>2018</x:v>
+      </x:c>
+      <x:c r="B22" s="6" t="str">
+        <x:v>room_revenue</x:v>
+      </x:c>
+      <x:c r="C22" s="18" t="str">
+        <x:v>6772.3</x:v>
+      </x:c>
+      <x:c r="D22" s="6" t="str">
+        <x:v>10k_cny</x:v>
+      </x:c>
+      <x:c r="E22" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F22" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G22" s="24" t="str">
+        <x:v>jizhou_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="H22" s="6" t="str">
+        <x:v>gov_jz_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="I22" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J22" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202211/W020250107625770490134.rar</x:v>
+      </x:c>
+      <x:c r="K22" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="16" t="str">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="B23" s="6" t="str">
+        <x:v>guest_rooms</x:v>
+      </x:c>
+      <x:c r="C23" s="18" t="str">
+        <x:v>1391</x:v>
+      </x:c>
+      <x:c r="D23" s="6" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="E23" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F23" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G23" s="24" t="str">
+        <x:v>jizhou_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="H23" s="6" t="str">
+        <x:v>gov_jz_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="I23" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J23" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202211/W020250107625770490134.rar</x:v>
+      </x:c>
+      <x:c r="K23" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="16" t="str">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="B24" s="6" t="str">
+        <x:v>beds</x:v>
+      </x:c>
+      <x:c r="C24" s="18" t="str">
+        <x:v>2600</x:v>
+      </x:c>
+      <x:c r="D24" s="6" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="E24" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F24" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G24" s="24" t="str">
+        <x:v>jizhou_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="H24" s="6" t="str">
+        <x:v>gov_jz_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="I24" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J24" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202211/W020250107625770490134.rar</x:v>
+      </x:c>
+      <x:c r="K24" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="16" t="str">
+        <x:v>2019</x:v>
+      </x:c>
+      <x:c r="B25" s="6" t="str">
+        <x:v>room_revenue</x:v>
+      </x:c>
+      <x:c r="C25" s="18" t="str">
+        <x:v>6538.4</x:v>
+      </x:c>
+      <x:c r="D25" s="6" t="str">
+        <x:v>10k_cny</x:v>
+      </x:c>
+      <x:c r="E25" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F25" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G25" s="24" t="str">
+        <x:v>jizhou_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="H25" s="6" t="str">
+        <x:v>gov_jz_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="I25" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J25" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202211/W020250107625770490134.rar</x:v>
+      </x:c>
+      <x:c r="K25" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="16" t="str">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="B26" s="6" t="str">
+        <x:v>guest_rooms</x:v>
+      </x:c>
+      <x:c r="C26" s="18" t="str">
+        <x:v>1441</x:v>
+      </x:c>
+      <x:c r="D26" s="6" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="E26" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F26" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G26" s="24" t="str">
+        <x:v>jizhou_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="H26" s="6" t="str">
+        <x:v>gov_jz_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="I26" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J26" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202211/W020250107625770490134.rar</x:v>
+      </x:c>
+      <x:c r="K26" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="16" t="str">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="B27" s="6" t="str">
+        <x:v>beds</x:v>
+      </x:c>
+      <x:c r="C27" s="18" t="str">
+        <x:v>2672</x:v>
+      </x:c>
+      <x:c r="D27" s="6" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="E27" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F27" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G27" s="24" t="str">
+        <x:v>jizhou_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="H27" s="6" t="str">
+        <x:v>gov_jz_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="I27" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J27" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202211/W020250107625770490134.rar</x:v>
+      </x:c>
+      <x:c r="K27" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="16" t="str">
+        <x:v>2020</x:v>
+      </x:c>
+      <x:c r="B28" s="6" t="str">
+        <x:v>room_revenue</x:v>
+      </x:c>
+      <x:c r="C28" s="18" t="str">
+        <x:v>6068</x:v>
+      </x:c>
+      <x:c r="D28" s="6" t="str">
+        <x:v>10k_cny</x:v>
+      </x:c>
+      <x:c r="E28" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F28" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G28" s="24" t="str">
+        <x:v>jizhou_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="H28" s="6" t="str">
+        <x:v>gov_jz_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="I28" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J28" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202211/W020250107625770490134.rar</x:v>
+      </x:c>
+      <x:c r="K28" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="16" t="str">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="B29" s="6" t="str">
+        <x:v>guest_rooms</x:v>
+      </x:c>
+      <x:c r="C29" s="18" t="str">
+        <x:v>1342</x:v>
+      </x:c>
+      <x:c r="D29" s="6" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="E29" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F29" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G29" s="24" t="str">
+        <x:v>jizhou_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="H29" s="6" t="str">
+        <x:v>gov_jz_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="I29" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J29" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202211/W020250107625770490134.rar</x:v>
+      </x:c>
+      <x:c r="K29" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="16" t="str">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="B30" s="6" t="str">
+        <x:v>beds</x:v>
+      </x:c>
+      <x:c r="C30" s="18" t="str">
+        <x:v>2474</x:v>
+      </x:c>
+      <x:c r="D30" s="6" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="E30" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F30" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G30" s="24" t="str">
+        <x:v>jizhou_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="H30" s="6" t="str">
+        <x:v>gov_jz_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="I30" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J30" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202211/W020250107625770490134.rar</x:v>
+      </x:c>
+      <x:c r="K30" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="16" t="str">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="B31" s="6" t="str">
+        <x:v>room_revenue</x:v>
+      </x:c>
+      <x:c r="C31" s="18" t="str">
+        <x:v>7125.6</x:v>
+      </x:c>
+      <x:c r="D31" s="6" t="str">
+        <x:v>10k_cny</x:v>
+      </x:c>
+      <x:c r="E31" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F31" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G31" s="24" t="str">
+        <x:v>jizhou_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="H31" s="6" t="str">
+        <x:v>gov_jz_yearbook_2021</x:v>
+      </x:c>
+      <x:c r="I31" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J31" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202211/W020250107625770490134.rar</x:v>
+      </x:c>
+      <x:c r="K31" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="16" t="str">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="B32" s="6" t="str">
+        <x:v>guest_rooms</x:v>
+      </x:c>
+      <x:c r="C32" s="18" t="str">
+        <x:v>1085</x:v>
+      </x:c>
+      <x:c r="D32" s="6" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="E32" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F32" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G32" s="24" t="str">
+        <x:v>jizhou_yearbook_2022</x:v>
+      </x:c>
+      <x:c r="H32" s="6" t="str">
+        <x:v>gov_jz_yearbook_2022</x:v>
+      </x:c>
+      <x:c r="I32" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J32" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202311/W020250107625663560312.pdf</x:v>
+      </x:c>
+      <x:c r="K32" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="16" t="str">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="B33" s="6" t="str">
+        <x:v>beds</x:v>
+      </x:c>
+      <x:c r="C33" s="18" t="str">
+        <x:v>1934</x:v>
+      </x:c>
+      <x:c r="D33" s="6" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="E33" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F33" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G33" s="24" t="str">
+        <x:v>jizhou_yearbook_2022</x:v>
+      </x:c>
+      <x:c r="H33" s="6" t="str">
+        <x:v>gov_jz_yearbook_2022</x:v>
+      </x:c>
+      <x:c r="I33" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J33" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202311/W020250107625663560312.pdf</x:v>
+      </x:c>
+      <x:c r="K33" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="16" t="str">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="B34" s="6" t="str">
+        <x:v>room_revenue</x:v>
+      </x:c>
+      <x:c r="C34" s="18" t="str">
+        <x:v>4632</x:v>
+      </x:c>
+      <x:c r="D34" s="6" t="str">
+        <x:v>10k_cny</x:v>
+      </x:c>
+      <x:c r="E34" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F34" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G34" s="24" t="str">
+        <x:v>jizhou_yearbook_2022</x:v>
+      </x:c>
+      <x:c r="H34" s="6" t="str">
+        <x:v>gov_jz_yearbook_2022</x:v>
+      </x:c>
+      <x:c r="I34" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J34" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202311/W020250107625663560312.pdf</x:v>
+      </x:c>
+      <x:c r="K34" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="16" t="str">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="B35" s="6" t="str">
+        <x:v>guest_rooms</x:v>
+      </x:c>
+      <x:c r="C35" s="18" t="str">
+        <x:v>1361</x:v>
+      </x:c>
+      <x:c r="D35" s="6" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="E35" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F35" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G35" s="24" t="str">
+        <x:v>jizhou_yearbook_2023</x:v>
+      </x:c>
+      <x:c r="H35" s="6" t="str">
+        <x:v>gov_jz_yearbook_2023</x:v>
+      </x:c>
+      <x:c r="I35" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J35" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202501/W020250103638170510358.pdf</x:v>
+      </x:c>
+      <x:c r="K35" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="16" t="str">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="B36" s="6" t="str">
+        <x:v>beds</x:v>
+      </x:c>
+      <x:c r="C36" s="18" t="str">
+        <x:v>2292</x:v>
+      </x:c>
+      <x:c r="D36" s="6" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="E36" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F36" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G36" s="24" t="str">
+        <x:v>jizhou_yearbook_2023</x:v>
+      </x:c>
+      <x:c r="H36" s="6" t="str">
+        <x:v>gov_jz_yearbook_2023</x:v>
+      </x:c>
+      <x:c r="I36" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J36" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202501/W020250103638170510358.pdf</x:v>
+      </x:c>
+      <x:c r="K36" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="16" t="str">
+        <x:v>2023</x:v>
+      </x:c>
+      <x:c r="B37" s="6" t="str">
+        <x:v>room_revenue</x:v>
+      </x:c>
+      <x:c r="C37" s="18" t="str">
+        <x:v>7053</x:v>
+      </x:c>
+      <x:c r="D37" s="6" t="str">
+        <x:v>10k_cny</x:v>
+      </x:c>
+      <x:c r="E37" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F37" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G37" s="24" t="str">
+        <x:v>jizhou_yearbook_2023</x:v>
+      </x:c>
+      <x:c r="H37" s="6" t="str">
+        <x:v>gov_jz_yearbook_2023</x:v>
+      </x:c>
+      <x:c r="I37" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J37" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202501/W020250103638170510358.pdf</x:v>
+      </x:c>
+      <x:c r="K37" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="16" t="str">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B38" s="6" t="str">
+        <x:v>guest_rooms</x:v>
+      </x:c>
+      <x:c r="C38" s="18" t="str">
+        <x:v>2178</x:v>
+      </x:c>
+      <x:c r="D38" s="6" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="E38" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F38" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G38" s="24" t="str">
+        <x:v>jizhou_yearbook_2024</x:v>
+      </x:c>
+      <x:c r="H38" s="6" t="str">
+        <x:v>gov_jz_yearbook_2024</x:v>
+      </x:c>
+      <x:c r="I38" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J38" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202511/W020251126560102082891.pdf</x:v>
+      </x:c>
+      <x:c r="K38" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="16" t="str">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B39" s="6" t="str">
+        <x:v>beds</x:v>
+      </x:c>
+      <x:c r="C39" s="18" t="str">
+        <x:v>3673</x:v>
+      </x:c>
+      <x:c r="D39" s="6" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="E39" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F39" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G39" s="24" t="str">
+        <x:v>jizhou_yearbook_2024</x:v>
+      </x:c>
+      <x:c r="H39" s="6" t="str">
+        <x:v>gov_jz_yearbook_2024</x:v>
+      </x:c>
+      <x:c r="I39" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J39" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202511/W020251126560102082891.pdf</x:v>
+      </x:c>
+      <x:c r="K39" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="16" t="str">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B40" s="6" t="str">
+        <x:v>room_revenue</x:v>
+      </x:c>
+      <x:c r="C40" s="18" t="str">
+        <x:v>7312</x:v>
+      </x:c>
+      <x:c r="D40" s="6" t="str">
+        <x:v>10k_cny</x:v>
+      </x:c>
+      <x:c r="E40" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F40" s="24" t="str">
+        <x:v>above_designated_size_accommodation_and_catering</x:v>
+      </x:c>
+      <x:c r="G40" s="24" t="str">
+        <x:v>jizhou_yearbook_2024</x:v>
+      </x:c>
+      <x:c r="H40" s="6" t="str">
+        <x:v>gov_jz_yearbook_2024</x:v>
+      </x:c>
+      <x:c r="I40" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J40" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/tjnb/202511/W020251126560102082891.pdf</x:v>
+      </x:c>
+      <x:c r="K40" s="34" t="str">
+        <x:v>限额以上住宿和餐饮业口径；不得代表全区住宿总供给</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="16" t="str">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B41" s="6" t="str">
+        <x:v>guest_rooms</x:v>
+      </x:c>
+      <x:c r="C41" s="18" t="str">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D41" s="6" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="E41" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F41" s="24" t="str">
+        <x:v>star_rated_hotels</x:v>
+      </x:c>
+      <x:c r="G41" s="24" t="str">
+        <x:v>tianjin_culture_tourism_2024</x:v>
+      </x:c>
+      <x:c r="H41" s="6" t="str">
+        <x:v>gov_tj_whly_star_hotels_2024</x:v>
+      </x:c>
+      <x:c r="I41" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J41" s="34" t="str">
+        <x:v>https://whly.tj.gov.cn/ZWGKYXXGK1640/ZFXXGK5456_1/FDZDGKNR5153/TJXX3610/202509/W020250912551107590041.xls</x:v>
+      </x:c>
+      <x:c r="K41" s="34" t="str">
+        <x:v>蓟州星级饭店分区表；该年数值均列五星级栏；不得与限上系列相加</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="16" t="str">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="B42" s="6" t="str">
+        <x:v>beds</x:v>
+      </x:c>
+      <x:c r="C42" s="18" t="str">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="D42" s="6" t="str">
+        <x:v>count</x:v>
+      </x:c>
+      <x:c r="E42" s="24" t="str">
+        <x:v>observed_yearbook</x:v>
+      </x:c>
+      <x:c r="F42" s="24" t="str">
+        <x:v>star_rated_hotels</x:v>
+      </x:c>
+      <x:c r="G42" s="24" t="str">
+        <x:v>tianjin_culture_tourism_2024</x:v>
+      </x:c>
+      <x:c r="H42" s="6" t="str">
+        <x:v>gov_tj_whly_star_hotels_2024</x:v>
+      </x:c>
+      <x:c r="I42" s="36" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J42" s="34" t="str">
+        <x:v>https://whly.tj.gov.cn/ZWGKYXXGK1640/ZFXXGK5456_1/FDZDGKNR5153/TJXX3610/202509/W020250912551107590041.xls</x:v>
+      </x:c>
+      <x:c r="K42" s="34" t="str">
+        <x:v>蓟州星级饭店分区表；该年数值均列五星级栏；不得与限上系列相加</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="37" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="17" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="27" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="34" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="30" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="72" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="64" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="14" t="str">
+        <x:v>起始年</x:v>
+      </x:c>
+      <x:c r="B1" s="14" t="str">
+        <x:v>结束年</x:v>
+      </x:c>
+      <x:c r="C1" s="14" t="str">
+        <x:v>指标</x:v>
+      </x:c>
+      <x:c r="D1" s="14" t="str">
+        <x:v>数值</x:v>
+      </x:c>
+      <x:c r="E1" s="14" t="str">
+        <x:v>单位</x:v>
+      </x:c>
+      <x:c r="F1" s="14" t="str">
+        <x:v>证据角色</x:v>
+      </x:c>
+      <x:c r="G1" s="14" t="str">
+        <x:v>来源ID</x:v>
+      </x:c>
+      <x:c r="H1" s="14" t="str">
+        <x:v>推导式/原文</x:v>
+      </x:c>
+      <x:c r="I1" s="14" t="str">
+        <x:v>模型用途</x:v>
+      </x:c>
+      <x:c r="J1" s="14" t="str">
+        <x:v>来源URL</x:v>
+      </x:c>
+      <x:c r="K1" s="14" t="str">
+        <x:v>备注</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="16" t="str">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="B2" s="16" t="str">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="str">
+        <x:v>visitor_arrivals</x:v>
+      </x:c>
+      <x:c r="D2" s="18" t="str">
+        <x:v>2691</x:v>
+      </x:c>
+      <x:c r="E2" s="6" t="str">
+        <x:v>10k_person_visits</x:v>
+      </x:c>
+      <x:c r="F2" s="27" t="str">
+        <x:v>secondary_reported_actual</x:v>
+      </x:c>
+      <x:c r="G2" s="6" t="str">
+        <x:v>media_itbear_jizhou_2025</x:v>
+      </x:c>
+      <x:c r="H2" s="34" t="str"/>
+      <x:c r="I2" s="38" t="str">
+        <x:v>sensitivity_only</x:v>
+      </x:c>
+      <x:c r="J2" s="34" t="str">
+        <x:v>https://www.itbear.com.cn/html/2026-04/1271544.html</x:v>
+      </x:c>
+      <x:c r="K2" s="34" t="str">
+        <x:v>媒体报道值；知网和两项区县数据库均未检出可直接替代的官方年度表</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="16" t="str">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="B3" s="16" t="str">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="C3" s="6" t="str">
+        <x:v>comprehensive_tourism_income_lower_bound</x:v>
+      </x:c>
+      <x:c r="D3" s="18" t="str">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="E3" s="6" t="str">
+        <x:v>100m_cny</x:v>
+      </x:c>
+      <x:c r="F3" s="27" t="str">
+        <x:v>secondary_threshold</x:v>
+      </x:c>
+      <x:c r="G3" s="6" t="str">
+        <x:v>media_itbear_jizhou_2025</x:v>
+      </x:c>
+      <x:c r="H3" s="34" t="str">
+        <x:v>原文为突破200亿元</x:v>
+      </x:c>
+      <x:c r="I3" s="38" t="str">
+        <x:v>constraint_only</x:v>
+      </x:c>
+      <x:c r="J3" s="34" t="str">
+        <x:v>https://www.itbear.com.cn/html/2026-04/1271544.html</x:v>
+      </x:c>
+      <x:c r="K3" s="34" t="str">
+        <x:v>仅为严格下界而非精确年度实际</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="16" t="str">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="str">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="C4" s="6" t="str">
+        <x:v>comprehensive_tourism_income</x:v>
+      </x:c>
+      <x:c r="D4" s="18" t="str">
+        <x:v>108.7866</x:v>
+      </x:c>
+      <x:c r="E4" s="6" t="str">
+        <x:v>100m_cny</x:v>
+      </x:c>
+      <x:c r="F4" s="27" t="str">
+        <x:v>algebraic_derived</x:v>
+      </x:c>
+      <x:c r="G4" s="6" t="str">
+        <x:v>gov_jz_report_2018</x:v>
+      </x:c>
+      <x:c r="H4" s="34" t="str">
+        <x:v>130/1.195</x:v>
+      </x:c>
+      <x:c r="I4" s="38" t="str">
+        <x:v>diagnostic_only</x:v>
+      </x:c>
+      <x:c r="J4" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/ZFGZBG_20201207/202012/t20201227_5203142.html</x:v>
+      </x:c>
+      <x:c r="K4" s="34" t="str">
+        <x:v>由2017年约130亿元及增长19.5%反推；输入均经取整；不得回填官方实际</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="16" t="str">
+        <x:v>2021</x:v>
+      </x:c>
+      <x:c r="B5" s="16" t="str">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="C5" s="6" t="str">
+        <x:v>visitor_arrivals_combined</x:v>
+      </x:c>
+      <x:c r="D5" s="18" t="str">
+        <x:v>2803</x:v>
+      </x:c>
+      <x:c r="E5" s="6" t="str">
+        <x:v>10k_person_visits</x:v>
+      </x:c>
+      <x:c r="F5" s="27" t="str">
+        <x:v>aggregate_residual</x:v>
+      </x:c>
+      <x:c r="G5" s="6" t="str">
+        <x:v>gov_jz_report_2026;media_itbear_jizhou_2025</x:v>
+      </x:c>
+      <x:c r="H5" s="34" t="str">
+        <x:v>10500-2363-2643-2691</x:v>
+      </x:c>
+      <x:c r="I5" s="38" t="str">
+        <x:v>constraint_only</x:v>
+      </x:c>
+      <x:c r="J5" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/ZFGZBG_20201207/202601/t20260121_7228239.html;https://www.itbear.com.cn/html/2026-04/1271544.html</x:v>
+      </x:c>
+      <x:c r="K5" s="34" t="str">
+        <x:v>依赖2025二手值且累计量有取整；不能拆分为2021和2022年度实际</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="16" t="str">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="B6" s="16" t="str">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="C6" s="6" t="str">
+        <x:v>comprehensive_tourism_income_combined</x:v>
+      </x:c>
+      <x:c r="D6" s="18" t="str">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="E6" s="6" t="str">
+        <x:v>100m_cny</x:v>
+      </x:c>
+      <x:c r="F6" s="27" t="str">
+        <x:v>aggregate_residual</x:v>
+      </x:c>
+      <x:c r="G6" s="6" t="str">
+        <x:v>gov_jz_report_2026</x:v>
+      </x:c>
+      <x:c r="H6" s="34" t="str">
+        <x:v>792.5-110-191.5-221</x:v>
+      </x:c>
+      <x:c r="I6" s="38" t="str">
+        <x:v>constraint_only</x:v>
+      </x:c>
+      <x:c r="J6" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/ZFGZBG_20201207/202601/t20260121_7228239.html</x:v>
+      </x:c>
+      <x:c r="K6" s="34" t="str">
+        <x:v>官方五年累计扣除已知年度后的约束余量；不能拆分为年度实际</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="16" t="str">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="B7" s="16" t="str">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="C7" s="6" t="str">
+        <x:v>comprehensive_tourism_income</x:v>
+      </x:c>
+      <x:c r="D7" s="18" t="str">
+        <x:v>55.7491</x:v>
+      </x:c>
+      <x:c r="E7" s="6" t="str">
+        <x:v>100m_cny</x:v>
+      </x:c>
+      <x:c r="F7" s="27" t="str">
+        <x:v>target_implied_baseline</x:v>
+      </x:c>
+      <x:c r="G7" s="6" t="str">
+        <x:v>gov_jz_report_2023</x:v>
+      </x:c>
+      <x:c r="H7" s="34" t="str">
+        <x:v>160/(1+1.87)</x:v>
+      </x:c>
+      <x:c r="I7" s="38" t="str">
+        <x:v>diagnostic_only</x:v>
+      </x:c>
+      <x:c r="J7" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/ZFGZBG_20201207/202301/t20230106_6070587.html</x:v>
+      </x:c>
+      <x:c r="K7" s="34" t="str">
+        <x:v>由2023年目标160亿元和目标增速187%隐含；不是2022年直接观测</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="16" t="str">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="B8" s="16" t="str">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="str">
+        <x:v>comprehensive_tourism_income</x:v>
+      </x:c>
+      <x:c r="D8" s="18" t="str">
+        <x:v>214.2509</x:v>
+      </x:c>
+      <x:c r="E8" s="6" t="str">
+        <x:v>100m_cny</x:v>
+      </x:c>
+      <x:c r="F8" s="27" t="str">
+        <x:v>constraint_scenario</x:v>
+      </x:c>
+      <x:c r="G8" s="6" t="str">
+        <x:v>gov_jz_report_2023;gov_jz_report_2026</x:v>
+      </x:c>
+      <x:c r="H8" s="34" t="str">
+        <x:v>270-160/(1+1.87)</x:v>
+      </x:c>
+      <x:c r="I8" s="38" t="str">
+        <x:v>diagnostic_only</x:v>
+      </x:c>
+      <x:c r="J8" s="34" t="str">
+        <x:v>https://www.tjjz.gov.cn/zwgk/ZFGZBG_20201207/202301/t20230106_6070587.html;https://www.tjjz.gov.cn/zwgk/ZFGZBG_20201207/202601/t20260121_7228239.html</x:v>
+      </x:c>
+      <x:c r="K8" s="34" t="str">
+        <x:v>把目标隐含基数与官方累计联立所得；仅作情景一致性校验且与突破200亿元相容</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -5577,7 +8159,7 @@
       <x:c r="E2" s="34" t="str">
         <x:v>data/raw/tj_2025_bulletin_browser.txt</x:v>
       </x:c>
-      <x:c r="F2" s="40" t="str">
+      <x:c r="F2" s="42" t="str">
         <x:v>downloaded_via_chrome_text</x:v>
       </x:c>
       <x:c r="G2" s="34" t="str">
@@ -5600,7 +8182,7 @@
       <x:c r="E3" s="34" t="str">
         <x:v>data/raw/tj_2024_yearbook_browser.txt</x:v>
       </x:c>
-      <x:c r="F3" s="40" t="str">
+      <x:c r="F3" s="42" t="str">
         <x:v>downloaded_via_chrome_text</x:v>
       </x:c>
       <x:c r="G3" s="34" t="str">
@@ -5623,7 +8205,7 @@
       <x:c r="E4" s="34" t="str">
         <x:v>data/raw/tj_historical_index_browser.txt</x:v>
       </x:c>
-      <x:c r="F4" s="40" t="str">
+      <x:c r="F4" s="42" t="str">
         <x:v>downloaded_via_chrome_text</x:v>
       </x:c>
       <x:c r="G4" s="34" t="str">
@@ -5646,7 +8228,7 @@
       <x:c r="E5" s="34" t="str">
         <x:v>data/raw/tj_2024_monthly_browser.txt</x:v>
       </x:c>
-      <x:c r="F5" s="40" t="str">
+      <x:c r="F5" s="42" t="str">
         <x:v>downloaded_via_chrome_text</x:v>
       </x:c>
       <x:c r="G5" s="34" t="str">
@@ -5669,7 +8251,7 @@
       <x:c r="E6" s="34" t="str">
         <x:v>data/raw/tj_tourism_search_browser.txt</x:v>
       </x:c>
-      <x:c r="F6" s="40" t="str">
+      <x:c r="F6" s="42" t="str">
         <x:v>downloaded_via_chrome_text</x:v>
       </x:c>
       <x:c r="G6" s="34" t="str">
@@ -5692,7 +8274,7 @@
       <x:c r="E7" s="34" t="str">
         <x:v>data/raw/government/data_release_index.html</x:v>
       </x:c>
-      <x:c r="F7" s="40" t="str">
+      <x:c r="F7" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G7" s="34" t="str">
@@ -5715,7 +8297,7 @@
       <x:c r="E8" s="34" t="str">
         <x:v>data/raw/government/government_report_2011.html</x:v>
       </x:c>
-      <x:c r="F8" s="40" t="str">
+      <x:c r="F8" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G8" s="34" t="str">
@@ -5738,7 +8320,7 @@
       <x:c r="E9" s="34" t="str">
         <x:v>data/raw/government/government_report_2012.html</x:v>
       </x:c>
-      <x:c r="F9" s="40" t="str">
+      <x:c r="F9" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G9" s="34" t="str">
@@ -5761,7 +8343,7 @@
       <x:c r="E10" s="34" t="str">
         <x:v>data/raw/government/government_report_2015.html</x:v>
       </x:c>
-      <x:c r="F10" s="40" t="str">
+      <x:c r="F10" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G10" s="34" t="str">
@@ -5784,7 +8366,7 @@
       <x:c r="E11" s="34" t="str">
         <x:v>data/raw/government/government_report_2016.html</x:v>
       </x:c>
-      <x:c r="F11" s="40" t="str">
+      <x:c r="F11" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G11" s="34" t="str">
@@ -5807,7 +8389,7 @@
       <x:c r="E12" s="34" t="str">
         <x:v>data/raw/government/government_report_2017.html</x:v>
       </x:c>
-      <x:c r="F12" s="40" t="str">
+      <x:c r="F12" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G12" s="34" t="str">
@@ -5830,7 +8412,7 @@
       <x:c r="E13" s="34" t="str">
         <x:v>data/raw/government/government_report_2018.html</x:v>
       </x:c>
-      <x:c r="F13" s="40" t="str">
+      <x:c r="F13" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G13" s="34" t="str">
@@ -5853,7 +8435,7 @@
       <x:c r="E14" s="34" t="str">
         <x:v>data/raw/government/government_report_2019.html</x:v>
       </x:c>
-      <x:c r="F14" s="40" t="str">
+      <x:c r="F14" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G14" s="34" t="str">
@@ -5876,7 +8458,7 @@
       <x:c r="E15" s="34" t="str">
         <x:v>data/raw/government/government_report_2020.html</x:v>
       </x:c>
-      <x:c r="F15" s="40" t="str">
+      <x:c r="F15" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G15" s="34" t="str">
@@ -5899,7 +8481,7 @@
       <x:c r="E16" s="34" t="str">
         <x:v>data/raw/government/government_report_2021.html</x:v>
       </x:c>
-      <x:c r="F16" s="40" t="str">
+      <x:c r="F16" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G16" s="34" t="str">
@@ -5922,7 +8504,7 @@
       <x:c r="E17" s="34" t="str">
         <x:v>data/raw/government/government_report_2022.html</x:v>
       </x:c>
-      <x:c r="F17" s="40" t="str">
+      <x:c r="F17" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G17" s="34" t="str">
@@ -5945,7 +8527,7 @@
       <x:c r="E18" s="34" t="str">
         <x:v>data/raw/government/government_report_2023.html</x:v>
       </x:c>
-      <x:c r="F18" s="40" t="str">
+      <x:c r="F18" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G18" s="34" t="str">
@@ -5968,7 +8550,7 @@
       <x:c r="E19" s="34" t="str">
         <x:v>data/raw/government/government_report_2024.html</x:v>
       </x:c>
-      <x:c r="F19" s="40" t="str">
+      <x:c r="F19" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G19" s="34" t="str">
@@ -5991,7 +8573,7 @@
       <x:c r="E20" s="34" t="str">
         <x:v>data/raw/government/government_report_2025.html</x:v>
       </x:c>
-      <x:c r="F20" s="40" t="str">
+      <x:c r="F20" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G20" s="34" t="str">
@@ -6014,7 +8596,7 @@
       <x:c r="E21" s="34" t="str">
         <x:v>data/raw/government/government_report_2026.html</x:v>
       </x:c>
-      <x:c r="F21" s="40" t="str">
+      <x:c r="F21" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G21" s="34" t="str">
@@ -6037,7 +8619,7 @@
       <x:c r="E22" s="34" t="str">
         <x:v>data/raw/government/statistical_summary_2011.html</x:v>
       </x:c>
-      <x:c r="F22" s="40" t="str">
+      <x:c r="F22" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G22" s="34" t="str">
@@ -6060,7 +8642,7 @@
       <x:c r="E23" s="34" t="str">
         <x:v>data/raw/government/tourism_statistics_2011.html</x:v>
       </x:c>
-      <x:c r="F23" s="40" t="str">
+      <x:c r="F23" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G23" s="34" t="str">
@@ -6083,7 +8665,7 @@
       <x:c r="E24" s="34" t="str">
         <x:v>data/raw/government/tourism_statistics_2014.html</x:v>
       </x:c>
-      <x:c r="F24" s="40" t="str">
+      <x:c r="F24" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G24" s="34" t="str">
@@ -6106,7 +8688,7 @@
       <x:c r="E25" s="34" t="str">
         <x:v>data/raw/government/tourism_statistics_2015.html</x:v>
       </x:c>
-      <x:c r="F25" s="40" t="str">
+      <x:c r="F25" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G25" s="34" t="str">
@@ -6129,7 +8711,7 @@
       <x:c r="E26" s="34" t="str">
         <x:v>data/raw/government/tourism_statistics_2016.html</x:v>
       </x:c>
-      <x:c r="F26" s="40" t="str">
+      <x:c r="F26" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G26" s="34" t="str">
@@ -6152,7 +8734,7 @@
       <x:c r="E27" s="34" t="str">
         <x:v>data/raw/government/tourism_statistics_2017.html</x:v>
       </x:c>
-      <x:c r="F27" s="40" t="str">
+      <x:c r="F27" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G27" s="34" t="str">
@@ -6175,7 +8757,7 @@
       <x:c r="E28" s="34" t="str">
         <x:v>data/raw/government/historical_official_cache_evidence.md</x:v>
       </x:c>
-      <x:c r="F28" s="40" t="str">
+      <x:c r="F28" s="42" t="str">
         <x:v>indexed_official_page_removed</x:v>
       </x:c>
       <x:c r="G28" s="34" t="str">
@@ -6198,7 +8780,7 @@
       <x:c r="E29" s="34" t="str">
         <x:v>data/raw/government/historical_official_cache_evidence.md</x:v>
       </x:c>
-      <x:c r="F29" s="40" t="str">
+      <x:c r="F29" s="42" t="str">
         <x:v>indexed_official_attachment_unavailable</x:v>
       </x:c>
       <x:c r="G29" s="34" t="str">
@@ -6221,7 +8803,7 @@
       <x:c r="E30" s="34" t="str">
         <x:v>data/raw/government/statistical_bulletin_2019.html</x:v>
       </x:c>
-      <x:c r="F30" s="40" t="str">
+      <x:c r="F30" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G30" s="34" t="str">
@@ -6244,7 +8826,7 @@
       <x:c r="E31" s="34" t="str">
         <x:v>data/raw/government/jizhou_2019_bulletin_page.html</x:v>
       </x:c>
-      <x:c r="F31" s="40" t="str">
+      <x:c r="F31" s="42" t="str">
         <x:v>downloaded_html_duplicate</x:v>
       </x:c>
       <x:c r="G31" s="34" t="str">
@@ -6267,7 +8849,7 @@
       <x:c r="E32" s="34" t="str">
         <x:v>data/raw/government/statistical_bulletin_2020.html</x:v>
       </x:c>
-      <x:c r="F32" s="40" t="str">
+      <x:c r="F32" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G32" s="34" t="str">
@@ -6290,7 +8872,7 @@
       <x:c r="E33" s="34" t="str">
         <x:v>data/raw/government/jizhou_2020_bulletin_yearbook_page.html</x:v>
       </x:c>
-      <x:c r="F33" s="40" t="str">
+      <x:c r="F33" s="42" t="str">
         <x:v>downloaded_html_duplicate</x:v>
       </x:c>
       <x:c r="G33" s="34" t="str">
@@ -6313,7 +8895,7 @@
       <x:c r="E34" s="34" t="str">
         <x:v>data/raw/government/jizhou_yearbook_2020_comprehensive.xls</x:v>
       </x:c>
-      <x:c r="F34" s="40" t="str">
+      <x:c r="F34" s="42" t="str">
         <x:v>downloaded_xls</x:v>
       </x:c>
       <x:c r="G34" s="34" t="str">
@@ -6336,7 +8918,7 @@
       <x:c r="E35" s="34" t="str">
         <x:v>data/raw/government/statistical_bulletin_2021.html</x:v>
       </x:c>
-      <x:c r="F35" s="40" t="str">
+      <x:c r="F35" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G35" s="34" t="str">
@@ -6359,7 +8941,7 @@
       <x:c r="E36" s="34" t="str">
         <x:v>data/raw/government/jizhou_2021_yearbook_page.html</x:v>
       </x:c>
-      <x:c r="F36" s="40" t="str">
+      <x:c r="F36" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G36" s="34" t="str">
@@ -6382,7 +8964,7 @@
       <x:c r="E37" s="34" t="str">
         <x:v>data/raw/government/jizhou_yearbook_2021.rar</x:v>
       </x:c>
-      <x:c r="F37" s="40" t="str">
+      <x:c r="F37" s="42" t="str">
         <x:v>downloaded_rar</x:v>
       </x:c>
       <x:c r="G37" s="34" t="str">
@@ -6405,7 +8987,7 @@
       <x:c r="E38" s="34" t="str">
         <x:v>data/raw/government/statistical_bulletin_2022.html</x:v>
       </x:c>
-      <x:c r="F38" s="40" t="str">
+      <x:c r="F38" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G38" s="34" t="str">
@@ -6428,7 +9010,7 @@
       <x:c r="E39" s="34" t="str">
         <x:v>data/raw/government/jizhou_2022_yearbook_page.html</x:v>
       </x:c>
-      <x:c r="F39" s="40" t="str">
+      <x:c r="F39" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G39" s="34" t="str">
@@ -6451,7 +9033,7 @@
       <x:c r="E40" s="34" t="str">
         <x:v>data/raw/government/jizhou_yearbook_2022.pdf</x:v>
       </x:c>
-      <x:c r="F40" s="40" t="str">
+      <x:c r="F40" s="42" t="str">
         <x:v>downloaded_pdf</x:v>
       </x:c>
       <x:c r="G40" s="34" t="str">
@@ -6474,7 +9056,7 @@
       <x:c r="E41" s="34" t="str">
         <x:v>data/raw/government/statistical_bulletin_2023.html</x:v>
       </x:c>
-      <x:c r="F41" s="40" t="str">
+      <x:c r="F41" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G41" s="34" t="str">
@@ -6497,7 +9079,7 @@
       <x:c r="E42" s="34" t="str">
         <x:v>data/raw/government/jizhou_2023_yearbook_page.html</x:v>
       </x:c>
-      <x:c r="F42" s="40" t="str">
+      <x:c r="F42" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G42" s="34" t="str">
@@ -6520,7 +9102,7 @@
       <x:c r="E43" s="34" t="str">
         <x:v>data/raw/government/jizhou_yearbook_2023.pdf</x:v>
       </x:c>
-      <x:c r="F43" s="40" t="str">
+      <x:c r="F43" s="42" t="str">
         <x:v>downloaded_pdf</x:v>
       </x:c>
       <x:c r="G43" s="34" t="str">
@@ -6543,7 +9125,7 @@
       <x:c r="E44" s="34" t="str">
         <x:v>data/raw/government/statistical_bulletin_2024.html</x:v>
       </x:c>
-      <x:c r="F44" s="40" t="str">
+      <x:c r="F44" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G44" s="34" t="str">
@@ -6566,7 +9148,7 @@
       <x:c r="E45" s="34" t="str">
         <x:v>data/raw/government/jizhou_2024_yearbook_page.html</x:v>
       </x:c>
-      <x:c r="F45" s="40" t="str">
+      <x:c r="F45" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G45" s="34" t="str">
@@ -6589,7 +9171,7 @@
       <x:c r="E46" s="34" t="str">
         <x:v>data/raw/government/jizhou_yearbook_2024.pdf</x:v>
       </x:c>
-      <x:c r="F46" s="40" t="str">
+      <x:c r="F46" s="42" t="str">
         <x:v>downloaded_pdf</x:v>
       </x:c>
       <x:c r="G46" s="34" t="str">
@@ -6612,7 +9194,7 @@
       <x:c r="E47" s="34" t="str">
         <x:v>data/raw/government/statistical_bulletin_2025.html</x:v>
       </x:c>
-      <x:c r="F47" s="40" t="str">
+      <x:c r="F47" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G47" s="34" t="str">
@@ -6635,7 +9217,7 @@
       <x:c r="E48" s="34" t="str">
         <x:v>data/raw/government/monthly_statistics_2024.html</x:v>
       </x:c>
-      <x:c r="F48" s="40" t="str">
+      <x:c r="F48" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G48" s="34" t="str">
@@ -6658,7 +9240,7 @@
       <x:c r="E49" s="34" t="str">
         <x:v>data/raw/government/tianjin_statistics/tj_yearbook_2011_jixian_basic.html</x:v>
       </x:c>
-      <x:c r="F49" s="40" t="str">
+      <x:c r="F49" s="42" t="str">
         <x:v>downloaded_html</x:v>
       </x:c>
       <x:c r="G49" s="34" t="str">
@@ -6681,7 +9263,7 @@
       <x:c r="E50" s="34" t="str">
         <x:v>data/raw/government/historical_official_cache_evidence.md</x:v>
       </x:c>
-      <x:c r="F50" s="40" t="str">
+      <x:c r="F50" s="42" t="str">
         <x:v>indexed_official_page_waf</x:v>
       </x:c>
       <x:c r="G50" s="34" t="str">
@@ -6704,7 +9286,7 @@
       <x:c r="E51" s="34" t="str">
         <x:v>data/raw/government/tianjin_statistics/tj_yearbook_2023_jizhou_basic.xls</x:v>
       </x:c>
-      <x:c r="F51" s="40" t="str">
+      <x:c r="F51" s="42" t="str">
         <x:v>downloaded_xls</x:v>
       </x:c>
       <x:c r="G51" s="34" t="str">
@@ -6727,7 +9309,7 @@
       <x:c r="E52" s="34" t="str">
         <x:v>data/raw/government/tianjin_statistics/tj_yearbook_2024_jizhou_basic.xls</x:v>
       </x:c>
-      <x:c r="F52" s="40" t="str">
+      <x:c r="F52" s="42" t="str">
         <x:v>downloaded_xls</x:v>
       </x:c>
       <x:c r="G52" s="34" t="str">
@@ -6750,7 +9332,7 @@
       <x:c r="E53" s="34" t="str">
         <x:v>data/raw/government/tianjin_statistics/tj_yearbook_2024_district_indicators.xls</x:v>
       </x:c>
-      <x:c r="F53" s="40" t="str">
+      <x:c r="F53" s="42" t="str">
         <x:v>downloaded_xls</x:v>
       </x:c>
       <x:c r="G53" s="34" t="str">
@@ -6773,7 +9355,7 @@
       <x:c r="E54" s="34" t="str">
         <x:v>data/raw/government/tianjin_statistics/tj_yearbook_2025_jizhou_basic.xls</x:v>
       </x:c>
-      <x:c r="F54" s="40" t="str">
+      <x:c r="F54" s="42" t="str">
         <x:v>downloaded_xls</x:v>
       </x:c>
       <x:c r="G54" s="34" t="str">
@@ -6796,7 +9378,7 @@
       <x:c r="E55" s="34" t="str">
         <x:v>data/raw/government/tianjin_statistics/tj_yearbook_2025_district_indicators.xls</x:v>
       </x:c>
-      <x:c r="F55" s="40" t="str">
+      <x:c r="F55" s="42" t="str">
         <x:v>downloaded_xls</x:v>
       </x:c>
       <x:c r="G55" s="34" t="str">
@@ -6819,7 +9401,7 @@
       <x:c r="E56" s="34" t="str">
         <x:v>data/raw/government/tianjin_culture_tourism/star_hotels_by_district_2024.xls</x:v>
       </x:c>
-      <x:c r="F56" s="40" t="str">
+      <x:c r="F56" s="42" t="str">
         <x:v>downloaded_xls</x:v>
       </x:c>
       <x:c r="G56" s="34" t="str">
@@ -6842,11 +9424,116 @@
       <x:c r="E57" s="34" t="str">
         <x:v>data/raw/government/tianjin_culture_tourism/key_a_scenic_spots_2021_2024.xls</x:v>
       </x:c>
-      <x:c r="F57" s="40" t="str">
+      <x:c r="F57" s="42" t="str">
         <x:v>downloaded_xls</x:v>
       </x:c>
       <x:c r="G57" s="34" t="str">
         <x:v>accessed=2026-08-17;结构校验数据非全区旅游总量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="6" t="str">
+        <x:v>db_nankai_catalog_20260817</x:v>
+      </x:c>
+      <x:c r="B58" s="6" t="str">
+        <x:v>南开大学图书馆数据库</x:v>
+      </x:c>
+      <x:c r="C58" s="34" t="str">
+        <x:v>数据库检索目录</x:v>
+      </x:c>
+      <x:c r="D58" s="34" t="str">
+        <x:v>https://lib.nankai.edu.cn/sjkjs_15469/list.htm</x:v>
+      </x:c>
+      <x:c r="E58" s="34" t="str"/>
+      <x:c r="F58" s="42" t="str">
+        <x:v>browser_verified_catalog</x:v>
+      </x:c>
+      <x:c r="G58" s="34" t="str">
+        <x:v>accessed=2026-08-17;用于筛选EPS中经网和国研网等可能数据库</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="6" t="str">
+        <x:v>db_cnki_jizhou_gap_20260817</x:v>
+      </x:c>
+      <x:c r="B59" s="6" t="str">
+        <x:v>知网中国经济社会大数据</x:v>
+      </x:c>
+      <x:c r="C59" s="34" t="str">
+        <x:v>蓟州旅游缺口检索</x:v>
+      </x:c>
+      <x:c r="D59" s="34" t="str">
+        <x:v>https://data.cnki.net/</x:v>
+      </x:c>
+      <x:c r="E59" s="34" t="str"/>
+      <x:c r="F59" s="42" t="str">
+        <x:v>browser_searched_no_direct_p0</x:v>
+      </x:c>
+      <x:c r="G59" s="34" t="str">
+        <x:v>accessed=2026-08-17;区县年度旅游分类和天津统计年鉴表均未检出缺失年度游客量或综合收入</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="6" t="str">
+        <x:v>db_eps_jizhou_macro_20260817</x:v>
+      </x:c>
+      <x:c r="B60" s="6" t="str">
+        <x:v>EPS数据平台</x:v>
+      </x:c>
+      <x:c r="C60" s="34" t="str">
+        <x:v>中国区域经济数据库年度分县</x:v>
+      </x:c>
+      <x:c r="D60" s="34" t="str">
+        <x:v>https://olap.epsnet.com.cn/</x:v>
+      </x:c>
+      <x:c r="E60" s="34" t="str"/>
+      <x:c r="F60" s="42" t="str">
+        <x:v>browser_verified_query_no_export</x:v>
+      </x:c>
+      <x:c r="G60" s="34" t="str">
+        <x:v>accessed=2026-08-17;cubeId=776;蓟州GDP和第三产业值与中经网一致;旅游库无区县总量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="6" t="str">
+        <x:v>db_cei_jizhou_macro_20260817</x:v>
+      </x:c>
+      <x:c r="B61" s="6" t="str">
+        <x:v>中经网统计数据库</x:v>
+      </x:c>
+      <x:c r="C61" s="34" t="str">
+        <x:v>县域年度库蓟州区宏观序列</x:v>
+      </x:c>
+      <x:c r="D61" s="34" t="str">
+        <x:v>https://ceidata.cei.cn/db</x:v>
+      </x:c>
+      <x:c r="E61" s="34" t="str"/>
+      <x:c r="F61" s="42" t="str">
+        <x:v>browser_verified_query_no_export</x:v>
+      </x:c>
+      <x:c r="G61" s="34" t="str">
+        <x:v>accessed=2026-08-17;南开大学集团用户入口;GDP和第三产业来源栏标注天津统计年鉴</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="6" t="str">
+        <x:v>media_itbear_jizhou_2025</x:v>
+      </x:c>
+      <x:c r="B62" s="6" t="str">
+        <x:v>二手媒体</x:v>
+      </x:c>
+      <x:c r="C62" s="34" t="str">
+        <x:v>2025年蓟州旅游接待量报道</x:v>
+      </x:c>
+      <x:c r="D62" s="34" t="str">
+        <x:v>https://www.itbear.com.cn/html/2026-04/1271544.html</x:v>
+      </x:c>
+      <x:c r="E62" s="34" t="str"/>
+      <x:c r="F62" s="42" t="str">
+        <x:v>secondary_media_reference</x:v>
+      </x:c>
+      <x:c r="G62" s="34" t="str">
+        <x:v>accessed=2026-08-17;报道游客量2691万人次且旅游收入突破200亿元;未作为官方年度实际</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6854,7 +9541,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -6865,20 +9552,20 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="56" t="str">
+      <x:c r="A1" s="58" t="str">
         <x:v>蓟州区旅游经济政府数据扩充版</x:v>
       </x:c>
-      <x:c r="B1" s="56"/>
-      <x:c r="C1" s="56"/>
-      <x:c r="D1" s="56"/>
+      <x:c r="B1" s="58"/>
+      <x:c r="C1" s="58"/>
+      <x:c r="D1" s="58"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="57" t="str">
-        <x:v>整理日期 2026-08-17｜实际、目标、累计、推导和修订版本已分开保存</x:v>
-      </x:c>
-      <x:c r="B2" s="57"/>
-      <x:c r="C2" s="57"/>
-      <x:c r="D2" s="57"/>
+      <x:c r="A2" s="59" t="str">
+        <x:v>整理日期 2026-08-17｜官方原件、授权数据库核验、目标、累计与推导值已分开保存</x:v>
+      </x:c>
+      <x:c r="B2" s="59"/>
+      <x:c r="C2" s="59"/>
+      <x:c r="D2" s="59"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="34"/>
@@ -6904,11 +9591,11 @@
       <x:c r="A5" s="34" t="str">
         <x:v>优选游客量</x:v>
       </x:c>
-      <x:c r="B5" s="58" t="n">
+      <x:c r="B5" s="60" t="n">
         <x:f>COUNT('年度主表'!B2:B17)</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C5" s="59" t="n">
+      <x:c r="C5" s="61" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D5" s="34" t="str">
@@ -6919,11 +9606,11 @@
       <x:c r="A6" s="34" t="str">
         <x:v>优选综合收入</x:v>
       </x:c>
-      <x:c r="B6" s="58" t="n">
+      <x:c r="B6" s="60" t="n">
         <x:f>COUNT('年度主表'!F2:F17)</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C6" s="59" t="n">
+      <x:c r="C6" s="61" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D6" s="34" t="str">
@@ -6934,30 +9621,30 @@
       <x:c r="A7" s="34" t="str">
         <x:v>优选GDP</x:v>
       </x:c>
-      <x:c r="B7" s="58" t="n">
+      <x:c r="B7" s="60" t="n">
         <x:f>COUNT('年度主表'!H2:H17)</x:f>
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C7" s="59" t="n">
         <x:v>16</x:v>
       </x:c>
+      <x:c r="C7" s="61" t="n">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="D7" s="34" t="str">
-        <x:v>2017缺值；部分早期年份为预计或推导</x:v>
+        <x:v>16年全覆盖；2012—2020已用天津统计年鉴回列值补齐</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="34" t="str">
         <x:v>优选第三产业增加值</x:v>
       </x:c>
-      <x:c r="B8" s="58" t="n">
+      <x:c r="B8" s="60" t="n">
         <x:f>COUNT('年度主表'!J2:J17)</x:f>
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C8" s="59" t="n">
         <x:v>16</x:v>
       </x:c>
+      <x:c r="C8" s="61" t="n">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="D8" s="34" t="str">
-        <x:v>2012、2015—2018仍有缺口</x:v>
+        <x:v>16年全覆盖；2012—2020已用天津统计年鉴回列值补齐</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -7071,87 +9758,87 @@
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="60" t="str">
+      <x:c r="A18" s="38" t="str">
         <x:v>年度游客量/综合收入</x:v>
       </x:c>
-      <x:c r="B18" s="60" t="str">
+      <x:c r="B18" s="38" t="str">
         <x:v>2020</x:v>
       </x:c>
-      <x:c r="C18" s="60" t="str">
+      <x:c r="C18" s="38" t="str">
         <x:v>未找到可靠公开年度总量</x:v>
       </x:c>
-      <x:c r="D18" s="60" t="str">
+      <x:c r="D18" s="38" t="str">
         <x:v>保留空白</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="60" t="str">
+      <x:c r="A19" s="38" t="str">
         <x:v>精确游客量</x:v>
       </x:c>
-      <x:c r="B19" s="60" t="str">
+      <x:c r="B19" s="38" t="str">
         <x:v>2021</x:v>
       </x:c>
-      <x:c r="C19" s="60" t="str">
+      <x:c r="C19" s="38" t="str">
         <x:v>仅找到综合收入110亿元</x:v>
       </x:c>
-      <x:c r="D19" s="60" t="str">
+      <x:c r="D19" s="38" t="str">
         <x:v>保留游客空白</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="60" t="str">
+      <x:c r="A20" s="38" t="str">
         <x:v>年度游客量/实际综合收入</x:v>
       </x:c>
-      <x:c r="B20" s="60" t="str">
+      <x:c r="B20" s="38" t="str">
         <x:v>2022</x:v>
       </x:c>
-      <x:c r="C20" s="60" t="str">
-        <x:v>2023报告为目标而非2022实际</x:v>
-      </x:c>
-      <x:c r="D20" s="60" t="str">
-        <x:v>保留空白</x:v>
+      <x:c r="C20" s="38" t="str">
+        <x:v>仅有累计余量和目标隐含基数</x:v>
+      </x:c>
+      <x:c r="D20" s="38" t="str">
+        <x:v>不得回填推导值</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="60" t="str">
-        <x:v>年度旅游实际</x:v>
-      </x:c>
-      <x:c r="B21" s="60" t="str">
+      <x:c r="A21" s="38" t="str">
+        <x:v>官方年度旅游实际</x:v>
+      </x:c>
+      <x:c r="B21" s="38" t="str">
         <x:v>2025</x:v>
       </x:c>
-      <x:c r="C21" s="60" t="str">
-        <x:v>仅有目标和十四五累计</x:v>
-      </x:c>
-      <x:c r="D21" s="60" t="str">
-        <x:v>排除目标值</x:v>
+      <x:c r="C21" s="38" t="str">
+        <x:v>二手报道2691万人次且收入突破200亿元</x:v>
+      </x:c>
+      <x:c r="D21" s="38" t="str">
+        <x:v>仅作敏感性证据</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="61" t="str">
+      <x:c r="A22" s="62" t="str">
         <x:v>旅游综合收入</x:v>
       </x:c>
-      <x:c r="B22" s="61" t="str">
+      <x:c r="B22" s="62" t="str">
         <x:v>2016</x:v>
       </x:c>
-      <x:c r="C22" s="61" t="str">
+      <x:c r="C22" s="62" t="str">
         <x:v>仅找到直接收入</x:v>
       </x:c>
-      <x:c r="D22" s="61" t="str">
+      <x:c r="D22" s="62" t="str">
         <x:v>不得按5倍自动冒充实测</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="61" t="str">
-        <x:v>最终宏观值</x:v>
-      </x:c>
-      <x:c r="B23" s="61" t="str">
-        <x:v>2012/2015—2018</x:v>
-      </x:c>
-      <x:c r="C23" s="61" t="str">
-        <x:v>部分为预计或推导</x:v>
-      </x:c>
-      <x:c r="D23" s="61" t="str">
-        <x:v>需继续查旧年鉴</x:v>
+      <x:c r="A23" s="62" t="str">
+        <x:v>连续政策/行为/全域供给</x:v>
+      </x:c>
+      <x:c r="B23" s="62" t="str">
+        <x:v>2012—2025</x:v>
+      </x:c>
+      <x:c r="C23" s="62" t="str">
+        <x:v>已有道路、财政和限上住宿锚点</x:v>
+      </x:c>
+      <x:c r="D23" s="62" t="str">
+        <x:v>补齐连续同口径序列</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -7193,13 +9880,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B27" s="34" t="str">
-        <x:v>官方页下线或旧站防护；目录/同URL索引复核</x:v>
+        <x:v>授权数据库展示原年鉴值或官方索引复核</x:v>
       </x:c>
       <x:c r="C27" s="34" t="str">
-        <x:v>最小证据记录</x:v>
+        <x:v>浏览器核验记录</x:v>
       </x:c>
       <x:c r="D27" s="34" t="str">
-        <x:v>稳健性分析</x:v>
+        <x:v>宏观主序列/稳健性</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -7217,10 +9904,18 @@
       </x:c>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="34"/>
-      <x:c r="B29" s="34"/>
-      <x:c r="C29" s="34"/>
-      <x:c r="D29" s="34"/>
+      <x:c r="A29" s="34" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B29" s="34" t="str">
+        <x:v>二手媒体转述或阈值</x:v>
+      </x:c>
+      <x:c r="C29" s="34" t="str">
+        <x:v>无官方原表</x:v>
+      </x:c>
+      <x:c r="D29" s="34" t="str">
+        <x:v>仅敏感性/约束</x:v>
+      </x:c>
     </x:row>
     <x:row r="30" ht="34" customHeight="1">
       <x:c r="A30" s="14" t="str">
@@ -7306,10 +10001,10 @@
         <x:v>蓟州区政府数据发布</x:v>
       </x:c>
       <x:c r="C36" s="14" t="str">
-        <x:v>天津统计年鉴</x:v>
+        <x:v>南开大学图书馆数据库目录</x:v>
       </x:c>
       <x:c r="D36" s="14" t="str">
-        <x:v>天津市文旅局统计</x:v>
+        <x:v>中经网统计数据库</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -7320,10 +10015,10 @@
         <x:v>https://www.tjjz.gov.cn/zwgk/sjfb/</x:v>
       </x:c>
       <x:c r="C37" s="34" t="str">
-        <x:v>https://stats.tj.gov.cn/tjsj_52032/tjnj/</x:v>
+        <x:v>https://lib.nankai.edu.cn/sjkjs_15469/list.htm</x:v>
       </x:c>
       <x:c r="D37" s="34" t="str">
-        <x:v>https://whly.tj.gov.cn/ZWGKYXXGK1640/ZFXXGK5456_1/FDZDGKNR5153/TJXX3610/</x:v>
+        <x:v>https://ceidata.cei.cn/db</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
